--- a/data/hr/output/recommendation/domain_mapping_review_sheet.xlsx
+++ b/data/hr/output/recommendation/domain_mapping_review_sheet.xlsx
@@ -15,7 +15,7 @@
     <sheet name="분야 기준" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">검수!$A$1:$Q$213</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">검수!$A$1:$Q$212</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">교차검수!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="599">
   <si>
     <t xml:space="preserve">분야–과정 연결 검수 시트</t>
   </si>
@@ -2734,15 +2734,6 @@
   </si>
   <si>
     <t xml:space="preserve">한국직장인교육센터평생교육원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUB_ABA20243001058355_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">농협은행 자산관리 전문역 양성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">한국금융연수원</t>
   </si>
   <si>
     <t xml:space="preserve">SQL_FASTCAMPUS_210569</t>
@@ -14359,7 +14350,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q213"/>
+  <dimension ref="A1:Q212"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -15188,7 +15179,7 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="15"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
@@ -15205,13 +15196,13 @@
         <v>128</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>54</v>
@@ -15239,10 +15230,10 @@
         <v>130</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>52</v>
@@ -15270,16 +15261,16 @@
         <v>59</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>133</v>
-      </c>
       <c r="E24" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>52</v>
@@ -15307,22 +15298,22 @@
         <v>63</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>135</v>
-      </c>
       <c r="E25" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>54</v>
@@ -15344,22 +15335,22 @@
         <v>47</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>137</v>
-      </c>
       <c r="E26" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>54</v>
@@ -15373,7 +15364,7 @@
       <c r="P26" s="14"/>
       <c r="Q26" s="15"/>
     </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="n">
         <v>26</v>
       </c>
@@ -15381,27 +15372,29 @@
         <v>55</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="E27" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="F27" s="12" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J27" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
@@ -15418,16 +15411,16 @@
         <v>59</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" s="12" t="s">
         <v>140</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>143</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>52</v>
@@ -15439,7 +15432,7 @@
         <v>94</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
@@ -15457,22 +15450,22 @@
         <v>63</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>145</v>
-      </c>
       <c r="E29" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>94</v>
@@ -15496,16 +15489,16 @@
         <v>47</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>147</v>
-      </c>
       <c r="E30" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>52</v>
@@ -15535,22 +15528,22 @@
         <v>55</v>
       </c>
       <c r="C31" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>149</v>
-      </c>
       <c r="E31" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>94</v>
@@ -15574,29 +15567,27 @@
         <v>59</v>
       </c>
       <c r="C32" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>151</v>
-      </c>
       <c r="E32" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>118</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J32" s="11"/>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
@@ -15605,7 +15596,7 @@
       <c r="P32" s="14"/>
       <c r="Q32" s="15"/>
     </row>
-    <row r="33" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="n">
         <v>32</v>
       </c>
@@ -15613,16 +15604,16 @@
         <v>63</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>142</v>
-      </c>
       <c r="F33" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>52</v>
@@ -15642,7 +15633,7 @@
       <c r="P33" s="14"/>
       <c r="Q33" s="15"/>
     </row>
-    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="n">
         <v>33</v>
       </c>
@@ -15652,14 +15643,14 @@
       <c r="C34" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>155</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>52</v>
@@ -15679,7 +15670,7 @@
       <c r="P34" s="14"/>
       <c r="Q34" s="15"/>
     </row>
-    <row r="35" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="n">
         <v>34</v>
       </c>
@@ -15687,22 +15678,22 @@
         <v>55</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="E35" s="12" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>54</v>
@@ -15724,22 +15715,22 @@
         <v>59</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>160</v>
-      </c>
       <c r="E36" s="12" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>54</v>
@@ -15753,7 +15744,7 @@
       <c r="P36" s="14"/>
       <c r="Q36" s="15"/>
     </row>
-    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="n">
         <v>36</v>
       </c>
@@ -15761,27 +15752,29 @@
         <v>63</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>162</v>
-      </c>
       <c r="E37" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J37" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="14"/>
@@ -15804,22 +15797,22 @@
         <v>164</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="K38" s="14"/>
       <c r="L38" s="14"/>
@@ -15837,28 +15830,28 @@
         <v>55</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E39" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
@@ -15868,7 +15861,7 @@
       <c r="P39" s="14"/>
       <c r="Q39" s="15"/>
     </row>
-    <row r="40" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="n">
         <v>39</v>
       </c>
@@ -15876,16 +15869,16 @@
         <v>59</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>52</v>
@@ -15894,10 +15887,10 @@
         <v>82</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="K40" s="14"/>
       <c r="L40" s="14"/>
@@ -15915,28 +15908,28 @@
         <v>63</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>173</v>
-      </c>
       <c r="E41" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K41" s="14"/>
       <c r="L41" s="14"/>
@@ -15946,7 +15939,7 @@
       <c r="P41" s="14"/>
       <c r="Q41" s="15"/>
     </row>
-    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="n">
         <v>41</v>
       </c>
@@ -15954,28 +15947,28 @@
         <v>47</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>175</v>
-      </c>
       <c r="E42" s="12" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
@@ -15985,7 +15978,7 @@
       <c r="P42" s="14"/>
       <c r="Q42" s="15"/>
     </row>
-    <row r="43" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="n">
         <v>42</v>
       </c>
@@ -15999,10 +15992,10 @@
         <v>177</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>52</v>
@@ -16011,7 +16004,7 @@
         <v>82</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>178</v>
@@ -16024,7 +16017,7 @@
       <c r="P43" s="14"/>
       <c r="Q43" s="15"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="n">
         <v>43</v>
       </c>
@@ -16034,7 +16027,7 @@
       <c r="C44" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="11" t="s">
         <v>180</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -16047,14 +16040,12 @@
         <v>52</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>181</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J44" s="11"/>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
@@ -16063,7 +16054,7 @@
       <c r="P44" s="14"/>
       <c r="Q44" s="15"/>
     </row>
-    <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="n">
         <v>44</v>
       </c>
@@ -16071,10 +16062,10 @@
         <v>63</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>182</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>74</v>
@@ -16086,12 +16077,14 @@
         <v>52</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J45" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
@@ -16108,10 +16101,10 @@
         <v>47</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>184</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>185</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>74</v>
@@ -16123,14 +16116,12 @@
         <v>52</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>118</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J46" s="11"/>
       <c r="K46" s="14"/>
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
@@ -16147,10 +16138,10 @@
         <v>55</v>
       </c>
       <c r="C47" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>187</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>74</v>
@@ -16176,7 +16167,7 @@
       <c r="P47" s="14"/>
       <c r="Q47" s="15"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
@@ -16184,10 +16175,10 @@
         <v>59</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>189</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>74</v>
@@ -16199,12 +16190,14 @@
         <v>52</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J48" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
@@ -16221,10 +16214,10 @@
         <v>63</v>
       </c>
       <c r="C49" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>191</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>74</v>
@@ -16260,10 +16253,10 @@
         <v>47</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>192</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>193</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>74</v>
@@ -16299,10 +16292,10 @@
         <v>55</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>195</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>74</v>
@@ -16330,7 +16323,7 @@
       <c r="P51" s="14"/>
       <c r="Q51" s="15"/>
     </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="n">
         <v>51</v>
       </c>
@@ -16338,10 +16331,10 @@
         <v>59</v>
       </c>
       <c r="C52" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D52" s="11" t="s">
         <v>196</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>197</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>74</v>
@@ -16377,10 +16370,10 @@
         <v>63</v>
       </c>
       <c r="C53" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>198</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>199</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>74</v>
@@ -16416,10 +16409,10 @@
         <v>47</v>
       </c>
       <c r="C54" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>200</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>201</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>74</v>
@@ -16455,10 +16448,10 @@
         <v>55</v>
       </c>
       <c r="C55" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>202</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>203</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>74</v>
@@ -16494,10 +16487,10 @@
         <v>59</v>
       </c>
       <c r="C56" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>205</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>74</v>
@@ -16533,10 +16526,10 @@
         <v>63</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>74</v>
@@ -16572,10 +16565,10 @@
         <v>47</v>
       </c>
       <c r="C58" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>209</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>74</v>
@@ -16611,10 +16604,10 @@
         <v>55</v>
       </c>
       <c r="C59" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>211</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>74</v>
@@ -16650,10 +16643,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D60" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>213</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>74</v>
@@ -16689,10 +16682,10 @@
         <v>63</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>215</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>74</v>
@@ -16728,10 +16721,10 @@
         <v>47</v>
       </c>
       <c r="C62" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D62" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>217</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>74</v>
@@ -16767,10 +16760,10 @@
         <v>55</v>
       </c>
       <c r="C63" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D63" s="11" t="s">
         <v>218</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>219</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>74</v>
@@ -16806,10 +16799,10 @@
         <v>59</v>
       </c>
       <c r="C64" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>74</v>
@@ -16845,10 +16838,10 @@
         <v>63</v>
       </c>
       <c r="C65" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D65" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="E65" s="12" t="s">
         <v>74</v>
@@ -16884,10 +16877,10 @@
         <v>47</v>
       </c>
       <c r="C66" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D66" s="11" t="s">
         <v>224</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>74</v>
@@ -16923,10 +16916,10 @@
         <v>55</v>
       </c>
       <c r="C67" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D67" s="11" t="s">
         <v>226</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>227</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>74</v>
@@ -16954,7 +16947,7 @@
       <c r="P67" s="14"/>
       <c r="Q67" s="15"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="n">
         <v>67</v>
       </c>
@@ -16962,10 +16955,10 @@
         <v>59</v>
       </c>
       <c r="C68" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D68" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>229</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>74</v>
@@ -17001,10 +16994,10 @@
         <v>63</v>
       </c>
       <c r="C69" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>231</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>74</v>
@@ -17040,10 +17033,10 @@
         <v>47</v>
       </c>
       <c r="C70" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D70" s="11" t="s">
         <v>232</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>233</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>74</v>
@@ -17071,7 +17064,7 @@
       <c r="P70" s="14"/>
       <c r="Q70" s="15"/>
     </row>
-    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="n">
         <v>70</v>
       </c>
@@ -17079,10 +17072,10 @@
         <v>55</v>
       </c>
       <c r="C71" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D71" s="11" t="s">
         <v>234</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>235</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>74</v>
@@ -17118,10 +17111,10 @@
         <v>59</v>
       </c>
       <c r="C72" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D72" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>237</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>74</v>
@@ -17157,10 +17150,10 @@
         <v>63</v>
       </c>
       <c r="C73" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>74</v>
@@ -17196,10 +17189,10 @@
         <v>47</v>
       </c>
       <c r="C74" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D74" s="11" t="s">
         <v>240</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>241</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>74</v>
@@ -17235,10 +17228,10 @@
         <v>55</v>
       </c>
       <c r="C75" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>74</v>
@@ -17274,10 +17267,10 @@
         <v>59</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>244</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>74</v>
@@ -17289,14 +17282,12 @@
         <v>52</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J76" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I76" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J76" s="11"/>
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
       <c r="M76" s="14"/>
@@ -17313,10 +17304,10 @@
         <v>63</v>
       </c>
       <c r="C77" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>246</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>74</v>
@@ -17328,12 +17319,14 @@
         <v>52</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I77" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J77" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>247</v>
+      </c>
       <c r="K77" s="14"/>
       <c r="L77" s="14"/>
       <c r="M77" s="14"/>
@@ -17365,13 +17358,13 @@
         <v>52</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="K78" s="14"/>
       <c r="L78" s="14"/>
@@ -17389,10 +17382,10 @@
         <v>55</v>
       </c>
       <c r="C79" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>251</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>252</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>74</v>
@@ -17404,14 +17397,12 @@
         <v>52</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J79" s="12" t="s">
-        <v>181</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J79" s="11"/>
       <c r="K79" s="14"/>
       <c r="L79" s="14"/>
       <c r="M79" s="14"/>
@@ -17428,10 +17419,10 @@
         <v>59</v>
       </c>
       <c r="C80" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D80" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>254</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>74</v>
@@ -17443,12 +17434,14 @@
         <v>52</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I80" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J80" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>247</v>
+      </c>
       <c r="K80" s="14"/>
       <c r="L80" s="14"/>
       <c r="M80" s="14"/>
@@ -17465,10 +17458,10 @@
         <v>63</v>
       </c>
       <c r="C81" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>255</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="E81" s="12" t="s">
         <v>74</v>
@@ -17486,7 +17479,7 @@
         <v>103</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K81" s="14"/>
       <c r="L81" s="14"/>
@@ -17504,10 +17497,10 @@
         <v>47</v>
       </c>
       <c r="C82" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>257</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>258</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>74</v>
@@ -17525,7 +17518,7 @@
         <v>103</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K82" s="14"/>
       <c r="L82" s="14"/>
@@ -17543,10 +17536,10 @@
         <v>55</v>
       </c>
       <c r="C83" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>260</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>74</v>
@@ -17558,13 +17551,13 @@
         <v>52</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="K83" s="14"/>
       <c r="L83" s="14"/>
@@ -17582,10 +17575,10 @@
         <v>59</v>
       </c>
       <c r="C84" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D84" s="12" t="s">
         <v>261</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>262</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>74</v>
@@ -17603,7 +17596,7 @@
         <v>108</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="K84" s="14"/>
       <c r="L84" s="14"/>
@@ -17636,13 +17629,13 @@
         <v>52</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="K85" s="14"/>
       <c r="L85" s="14"/>
@@ -17660,10 +17653,10 @@
         <v>47</v>
       </c>
       <c r="C86" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D86" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>267</v>
       </c>
       <c r="E86" s="12" t="s">
         <v>74</v>
@@ -17675,14 +17668,12 @@
         <v>52</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J86" s="12" t="s">
-        <v>250</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J86" s="11"/>
       <c r="K86" s="14"/>
       <c r="L86" s="14"/>
       <c r="M86" s="14"/>
@@ -17691,7 +17682,7 @@
       <c r="P86" s="14"/>
       <c r="Q86" s="15"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="n">
         <v>86</v>
       </c>
@@ -17699,10 +17690,10 @@
         <v>55</v>
       </c>
       <c r="C87" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>268</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="E87" s="12" t="s">
         <v>74</v>
@@ -17728,7 +17719,7 @@
       <c r="P87" s="14"/>
       <c r="Q87" s="15"/>
     </row>
-    <row r="88" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="n">
         <v>87</v>
       </c>
@@ -17736,10 +17727,10 @@
         <v>59</v>
       </c>
       <c r="C88" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E88" s="12" t="s">
         <v>74</v>
@@ -17773,10 +17764,10 @@
         <v>63</v>
       </c>
       <c r="C89" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>273</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>74</v>
@@ -17788,12 +17779,14 @@
         <v>52</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I89" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J89" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="K89" s="14"/>
       <c r="L89" s="14"/>
       <c r="M89" s="14"/>
@@ -17810,10 +17803,10 @@
         <v>47</v>
       </c>
       <c r="C90" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>74</v>
@@ -17831,7 +17824,7 @@
         <v>108</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K90" s="14"/>
       <c r="L90" s="14"/>
@@ -17849,10 +17842,10 @@
         <v>55</v>
       </c>
       <c r="C91" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D91" s="12" t="s">
         <v>276</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="E91" s="12" t="s">
         <v>74</v>
@@ -17870,7 +17863,7 @@
         <v>108</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="K91" s="14"/>
       <c r="L91" s="14"/>
@@ -17888,10 +17881,10 @@
         <v>59</v>
       </c>
       <c r="C92" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="D92" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>74</v>
@@ -17906,10 +17899,10 @@
         <v>82</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="K92" s="14"/>
       <c r="L92" s="14"/>
@@ -17927,10 +17920,10 @@
         <v>63</v>
       </c>
       <c r="C93" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D93" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>281</v>
       </c>
       <c r="E93" s="12" t="s">
         <v>74</v>
@@ -17945,10 +17938,10 @@
         <v>82</v>
       </c>
       <c r="I93" s="12" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="K93" s="14"/>
       <c r="L93" s="14"/>
@@ -17966,10 +17959,10 @@
         <v>47</v>
       </c>
       <c r="C94" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D94" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>283</v>
       </c>
       <c r="E94" s="12" t="s">
         <v>74</v>
@@ -17984,10 +17977,10 @@
         <v>82</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K94" s="14"/>
       <c r="L94" s="14"/>
@@ -17997,7 +17990,7 @@
       <c r="P94" s="14"/>
       <c r="Q94" s="15"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="11" t="n">
         <v>94</v>
       </c>
@@ -18005,10 +17998,10 @@
         <v>55</v>
       </c>
       <c r="C95" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D95" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>285</v>
       </c>
       <c r="E95" s="12" t="s">
         <v>74</v>
@@ -18020,13 +18013,13 @@
         <v>52</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="K95" s="14"/>
       <c r="L95" s="14"/>
@@ -18059,14 +18052,12 @@
         <v>52</v>
       </c>
       <c r="H96" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J96" s="12" t="s">
-        <v>288</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I96" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J96" s="11"/>
       <c r="K96" s="14"/>
       <c r="L96" s="14"/>
       <c r="M96" s="14"/>
@@ -18083,10 +18074,10 @@
         <v>63</v>
       </c>
       <c r="C97" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>289</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>290</v>
       </c>
       <c r="E97" s="12" t="s">
         <v>74</v>
@@ -18098,7 +18089,7 @@
         <v>52</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>54</v>
@@ -18120,10 +18111,10 @@
         <v>47</v>
       </c>
       <c r="C98" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" s="11" t="s">
         <v>291</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>292</v>
       </c>
       <c r="E98" s="12" t="s">
         <v>74</v>
@@ -18135,7 +18126,7 @@
         <v>52</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>54</v>
@@ -18149,7 +18140,7 @@
       <c r="P98" s="14"/>
       <c r="Q98" s="15"/>
     </row>
-    <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="11" t="n">
         <v>98</v>
       </c>
@@ -18157,10 +18148,10 @@
         <v>55</v>
       </c>
       <c r="C99" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" s="11" t="s">
         <v>293</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>294</v>
       </c>
       <c r="E99" s="12" t="s">
         <v>74</v>
@@ -18194,10 +18185,10 @@
         <v>59</v>
       </c>
       <c r="C100" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>295</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>296</v>
       </c>
       <c r="E100" s="12" t="s">
         <v>74</v>
@@ -18211,10 +18202,12 @@
       <c r="H100" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I100" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J100" s="11"/>
+      <c r="I100" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>297</v>
+      </c>
       <c r="K100" s="14"/>
       <c r="L100" s="14"/>
       <c r="M100" s="14"/>
@@ -18223,7 +18216,7 @@
       <c r="P100" s="14"/>
       <c r="Q100" s="15"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="n">
         <v>100</v>
       </c>
@@ -18231,10 +18224,10 @@
         <v>63</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E101" s="12" t="s">
         <v>74</v>
@@ -18246,14 +18239,12 @@
         <v>52</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I101" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>300</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I101" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J101" s="11"/>
       <c r="K101" s="14"/>
       <c r="L101" s="14"/>
       <c r="M101" s="14"/>
@@ -18262,7 +18253,7 @@
       <c r="P101" s="14"/>
       <c r="Q101" s="15"/>
     </row>
-    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="11" t="n">
         <v>101</v>
       </c>
@@ -18270,27 +18261,29 @@
         <v>47</v>
       </c>
       <c r="C102" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="D102" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="E102" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="E102" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="F102" s="12" t="s">
-        <v>74</v>
+        <v>303</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I102" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J102" s="11"/>
+        <v>58</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>304</v>
+      </c>
       <c r="K102" s="14"/>
       <c r="L102" s="14"/>
       <c r="M102" s="14"/>
@@ -18299,7 +18292,7 @@
       <c r="P102" s="14"/>
       <c r="Q102" s="15"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="11" t="n">
         <v>102</v>
       </c>
@@ -18307,16 +18300,16 @@
         <v>55</v>
       </c>
       <c r="C103" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="F103" s="12" t="s">
         <v>303</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>306</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>52</v>
@@ -18325,10 +18318,10 @@
         <v>58</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J103" s="12" t="s">
-        <v>307</v>
+        <v>296</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="K103" s="14"/>
       <c r="L103" s="14"/>
@@ -18346,16 +18339,16 @@
         <v>59</v>
       </c>
       <c r="C104" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D104" s="11" t="s">
-        <v>309</v>
-      </c>
       <c r="E104" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>52</v>
@@ -18364,10 +18357,10 @@
         <v>58</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K104" s="14"/>
       <c r="L104" s="14"/>
@@ -18377,7 +18370,7 @@
       <c r="P104" s="14"/>
       <c r="Q104" s="15"/>
     </row>
-    <row r="105" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="11" t="n">
         <v>104</v>
       </c>
@@ -18385,28 +18378,28 @@
         <v>63</v>
       </c>
       <c r="C105" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="D105" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D105" s="11" t="s">
-        <v>311</v>
-      </c>
       <c r="E105" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G105" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J105" s="11" t="s">
-        <v>300</v>
+        <v>103</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="K105" s="14"/>
       <c r="L105" s="14"/>
@@ -18416,7 +18409,7 @@
       <c r="P105" s="14"/>
       <c r="Q105" s="15"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="11" t="n">
         <v>105</v>
       </c>
@@ -18424,16 +18417,16 @@
         <v>47</v>
       </c>
       <c r="C106" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D106" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="D106" s="11" t="s">
-        <v>313</v>
-      </c>
       <c r="E106" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G106" s="13" t="s">
         <v>52</v>
@@ -18445,7 +18438,7 @@
         <v>103</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K106" s="14"/>
       <c r="L106" s="14"/>
@@ -18455,7 +18448,7 @@
       <c r="P106" s="14"/>
       <c r="Q106" s="15"/>
     </row>
-    <row r="107" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="11" t="n">
         <v>106</v>
       </c>
@@ -18463,28 +18456,28 @@
         <v>55</v>
       </c>
       <c r="C107" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="D107" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="D107" s="11" t="s">
-        <v>315</v>
-      </c>
       <c r="E107" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G107" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="K107" s="14"/>
       <c r="L107" s="14"/>
@@ -18494,7 +18487,7 @@
       <c r="P107" s="14"/>
       <c r="Q107" s="15"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="n">
         <v>107</v>
       </c>
@@ -18502,29 +18495,27 @@
         <v>59</v>
       </c>
       <c r="C108" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D108" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="D108" s="11" t="s">
-        <v>317</v>
-      </c>
       <c r="E108" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G108" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I108" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J108" s="12" t="s">
-        <v>181</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I108" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J108" s="11"/>
       <c r="K108" s="14"/>
       <c r="L108" s="14"/>
       <c r="M108" s="14"/>
@@ -18533,7 +18524,7 @@
       <c r="P108" s="14"/>
       <c r="Q108" s="15"/>
     </row>
-    <row r="109" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="n">
         <v>108</v>
       </c>
@@ -18541,16 +18532,16 @@
         <v>63</v>
       </c>
       <c r="C109" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="D109" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D109" s="11" t="s">
-        <v>319</v>
-      </c>
       <c r="E109" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G109" s="13" t="s">
         <v>52</v>
@@ -18570,7 +18561,7 @@
       <c r="P109" s="14"/>
       <c r="Q109" s="15"/>
     </row>
-    <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="11" t="n">
         <v>109</v>
       </c>
@@ -18578,16 +18569,16 @@
         <v>47</v>
       </c>
       <c r="C110" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D110" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="D110" s="11" t="s">
-        <v>321</v>
-      </c>
       <c r="E110" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G110" s="13" t="s">
         <v>52</v>
@@ -18607,7 +18598,7 @@
       <c r="P110" s="14"/>
       <c r="Q110" s="15"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="11" t="n">
         <v>110</v>
       </c>
@@ -18615,16 +18606,16 @@
         <v>55</v>
       </c>
       <c r="C111" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D111" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D111" s="11" t="s">
-        <v>323</v>
-      </c>
       <c r="E111" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G111" s="13" t="s">
         <v>52</v>
@@ -18644,7 +18635,7 @@
       <c r="P111" s="14"/>
       <c r="Q111" s="15"/>
     </row>
-    <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="11" t="n">
         <v>111</v>
       </c>
@@ -18652,16 +18643,16 @@
         <v>59</v>
       </c>
       <c r="C112" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D112" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D112" s="11" t="s">
-        <v>325</v>
-      </c>
       <c r="E112" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G112" s="13" t="s">
         <v>52</v>
@@ -18681,7 +18672,7 @@
       <c r="P112" s="14"/>
       <c r="Q112" s="15"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="n">
         <v>112</v>
       </c>
@@ -18689,16 +18680,16 @@
         <v>63</v>
       </c>
       <c r="C113" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="D113" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="D113" s="11" t="s">
-        <v>327</v>
-      </c>
       <c r="E113" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>52</v>
@@ -18718,7 +18709,7 @@
       <c r="P113" s="14"/>
       <c r="Q113" s="15"/>
     </row>
-    <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="n">
         <v>113</v>
       </c>
@@ -18726,16 +18717,16 @@
         <v>47</v>
       </c>
       <c r="C114" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="D114" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="D114" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="E114" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G114" s="13" t="s">
         <v>52</v>
@@ -18763,16 +18754,16 @@
         <v>55</v>
       </c>
       <c r="C115" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="D115" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="D115" s="11" t="s">
-        <v>331</v>
-      </c>
       <c r="E115" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G115" s="13" t="s">
         <v>52</v>
@@ -18792,7 +18783,7 @@
       <c r="P115" s="14"/>
       <c r="Q115" s="15"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="11" t="n">
         <v>115</v>
       </c>
@@ -18800,16 +18791,16 @@
         <v>59</v>
       </c>
       <c r="C116" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D116" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="D116" s="11" t="s">
-        <v>333</v>
-      </c>
       <c r="E116" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G116" s="13" t="s">
         <v>52</v>
@@ -18829,7 +18820,7 @@
       <c r="P116" s="14"/>
       <c r="Q116" s="15"/>
     </row>
-    <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="11" t="n">
         <v>116</v>
       </c>
@@ -18837,16 +18828,16 @@
         <v>63</v>
       </c>
       <c r="C117" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D117" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="D117" s="11" t="s">
-        <v>335</v>
-      </c>
       <c r="E117" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G117" s="13" t="s">
         <v>52</v>
@@ -18866,7 +18857,7 @@
       <c r="P117" s="14"/>
       <c r="Q117" s="15"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="11" t="n">
         <v>117</v>
       </c>
@@ -18874,16 +18865,16 @@
         <v>47</v>
       </c>
       <c r="C118" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="D118" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="D118" s="11" t="s">
-        <v>337</v>
-      </c>
       <c r="E118" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G118" s="13" t="s">
         <v>52</v>
@@ -18903,7 +18894,7 @@
       <c r="P118" s="14"/>
       <c r="Q118" s="15"/>
     </row>
-    <row r="119" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="11" t="n">
         <v>118</v>
       </c>
@@ -18911,16 +18902,16 @@
         <v>55</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D119" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="D119" s="11" t="s">
-        <v>339</v>
-      </c>
       <c r="E119" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G119" s="13" t="s">
         <v>52</v>
@@ -18940,7 +18931,7 @@
       <c r="P119" s="14"/>
       <c r="Q119" s="15"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="11" t="n">
         <v>119</v>
       </c>
@@ -18948,16 +18939,16 @@
         <v>59</v>
       </c>
       <c r="C120" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="D120" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="D120" s="11" t="s">
-        <v>341</v>
-      </c>
       <c r="E120" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F120" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G120" s="13" t="s">
         <v>52</v>
@@ -18977,7 +18968,7 @@
       <c r="P120" s="14"/>
       <c r="Q120" s="15"/>
     </row>
-    <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="11" t="n">
         <v>120</v>
       </c>
@@ -18985,16 +18976,16 @@
         <v>63</v>
       </c>
       <c r="C121" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D121" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="D121" s="11" t="s">
-        <v>343</v>
-      </c>
       <c r="E121" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G121" s="13" t="s">
         <v>52</v>
@@ -19022,16 +19013,16 @@
         <v>47</v>
       </c>
       <c r="C122" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D122" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="D122" s="11" t="s">
-        <v>345</v>
-      </c>
       <c r="E122" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F122" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G122" s="13" t="s">
         <v>52</v>
@@ -19059,16 +19050,16 @@
         <v>55</v>
       </c>
       <c r="C123" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D123" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="D123" s="11" t="s">
-        <v>347</v>
-      </c>
       <c r="E123" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F123" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G123" s="13" t="s">
         <v>52</v>
@@ -19096,16 +19087,16 @@
         <v>59</v>
       </c>
       <c r="C124" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D124" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D124" s="11" t="s">
-        <v>349</v>
-      </c>
       <c r="E124" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F124" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G124" s="13" t="s">
         <v>52</v>
@@ -19133,16 +19124,16 @@
         <v>63</v>
       </c>
       <c r="C125" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D125" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D125" s="11" t="s">
-        <v>351</v>
-      </c>
       <c r="E125" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G125" s="13" t="s">
         <v>52</v>
@@ -19170,16 +19161,16 @@
         <v>47</v>
       </c>
       <c r="C126" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="D126" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="D126" s="11" t="s">
-        <v>353</v>
-      </c>
       <c r="E126" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G126" s="13" t="s">
         <v>52</v>
@@ -19199,7 +19190,7 @@
       <c r="P126" s="14"/>
       <c r="Q126" s="15"/>
     </row>
-    <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="11" t="n">
         <v>126</v>
       </c>
@@ -19207,16 +19198,16 @@
         <v>55</v>
       </c>
       <c r="C127" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="D127" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="D127" s="11" t="s">
-        <v>355</v>
-      </c>
       <c r="E127" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F127" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G127" s="13" t="s">
         <v>52</v>
@@ -19236,7 +19227,7 @@
       <c r="P127" s="14"/>
       <c r="Q127" s="15"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="11" t="n">
         <v>127</v>
       </c>
@@ -19244,16 +19235,16 @@
         <v>59</v>
       </c>
       <c r="C128" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D128" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D128" s="11" t="s">
-        <v>357</v>
-      </c>
       <c r="E128" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G128" s="13" t="s">
         <v>52</v>
@@ -19273,7 +19264,7 @@
       <c r="P128" s="14"/>
       <c r="Q128" s="15"/>
     </row>
-    <row r="129" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="11" t="n">
         <v>128</v>
       </c>
@@ -19281,16 +19272,16 @@
         <v>63</v>
       </c>
       <c r="C129" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="D129" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="D129" s="11" t="s">
-        <v>359</v>
-      </c>
       <c r="E129" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G129" s="13" t="s">
         <v>52</v>
@@ -19298,10 +19289,12 @@
       <c r="H129" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I129" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J129" s="11"/>
+      <c r="I129" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>297</v>
+      </c>
       <c r="K129" s="14"/>
       <c r="L129" s="14"/>
       <c r="M129" s="14"/>
@@ -19310,7 +19303,7 @@
       <c r="P129" s="14"/>
       <c r="Q129" s="15"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="11" t="n">
         <v>129</v>
       </c>
@@ -19318,16 +19311,16 @@
         <v>47</v>
       </c>
       <c r="C130" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="D130" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="D130" s="11" t="s">
-        <v>361</v>
-      </c>
       <c r="E130" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G130" s="13" t="s">
         <v>52</v>
@@ -19336,10 +19329,10 @@
         <v>58</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>299</v>
+        <v>361</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="K130" s="14"/>
       <c r="L130" s="14"/>
@@ -19357,27 +19350,27 @@
         <v>55</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G131" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="J131" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="J131" s="12" t="s">
         <v>365</v>
       </c>
       <c r="K131" s="14"/>
@@ -19388,7 +19381,7 @@
       <c r="P131" s="14"/>
       <c r="Q131" s="15"/>
     </row>
-    <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="11" t="n">
         <v>131</v>
       </c>
@@ -19402,22 +19395,22 @@
         <v>367</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G132" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>368</v>
+        <v>162</v>
       </c>
       <c r="K132" s="14"/>
       <c r="L132" s="14"/>
@@ -19435,16 +19428,16 @@
         <v>63</v>
       </c>
       <c r="C133" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D133" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="D133" s="11" t="s">
-        <v>370</v>
-      </c>
       <c r="E133" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G133" s="13" t="s">
         <v>52</v>
@@ -19456,7 +19449,7 @@
         <v>108</v>
       </c>
       <c r="J133" s="12" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="K133" s="14"/>
       <c r="L133" s="14"/>
@@ -19474,16 +19467,16 @@
         <v>47</v>
       </c>
       <c r="C134" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="D134" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="D134" s="11" t="s">
-        <v>372</v>
-      </c>
       <c r="E134" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G134" s="13" t="s">
         <v>52</v>
@@ -19495,7 +19488,7 @@
         <v>108</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>109</v>
+        <v>372</v>
       </c>
       <c r="K134" s="14"/>
       <c r="L134" s="14"/>
@@ -19505,7 +19498,7 @@
       <c r="P134" s="14"/>
       <c r="Q134" s="15"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="11" t="n">
         <v>134</v>
       </c>
@@ -19519,19 +19512,19 @@
         <v>374</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G135" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J135" s="12" t="s">
         <v>375</v>
@@ -19558,22 +19551,22 @@
         <v>377</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G136" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="K136" s="14"/>
       <c r="L136" s="14"/>
@@ -19583,7 +19576,7 @@
       <c r="P136" s="14"/>
       <c r="Q136" s="15"/>
     </row>
-    <row r="137" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="11" t="n">
         <v>136</v>
       </c>
@@ -19591,28 +19584,28 @@
         <v>63</v>
       </c>
       <c r="C137" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="D137" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="D137" s="11" t="s">
-        <v>380</v>
-      </c>
       <c r="E137" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G137" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K137" s="14"/>
       <c r="L137" s="14"/>
@@ -19630,16 +19623,16 @@
         <v>47</v>
       </c>
       <c r="C138" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="D138" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D138" s="11" t="s">
-        <v>382</v>
-      </c>
       <c r="E138" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F138" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G138" s="13" t="s">
         <v>52</v>
@@ -19651,7 +19644,7 @@
         <v>108</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K138" s="14"/>
       <c r="L138" s="14"/>
@@ -19661,7 +19654,7 @@
       <c r="P138" s="14"/>
       <c r="Q138" s="15"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="11" t="n">
         <v>138</v>
       </c>
@@ -19669,29 +19662,27 @@
         <v>55</v>
       </c>
       <c r="C139" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="D139" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D139" s="11" t="s">
-        <v>384</v>
-      </c>
       <c r="E139" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F139" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G139" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I139" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J139" s="12" t="s">
-        <v>375</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I139" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J139" s="11"/>
       <c r="K139" s="14"/>
       <c r="L139" s="14"/>
       <c r="M139" s="14"/>
@@ -19700,7 +19691,7 @@
       <c r="P139" s="14"/>
       <c r="Q139" s="15"/>
     </row>
-    <row r="140" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="11" t="n">
         <v>139</v>
       </c>
@@ -19708,16 +19699,16 @@
         <v>59</v>
       </c>
       <c r="C140" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D140" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="D140" s="11" t="s">
+      <c r="E140" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="E140" s="12" t="s">
-        <v>305</v>
-      </c>
       <c r="F140" s="12" t="s">
-        <v>306</v>
+        <v>387</v>
       </c>
       <c r="G140" s="13" t="s">
         <v>52</v>
@@ -19745,16 +19736,16 @@
         <v>63</v>
       </c>
       <c r="C141" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F141" s="12" t="s">
         <v>387</v>
-      </c>
-      <c r="D141" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="E141" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="F141" s="12" t="s">
-        <v>390</v>
       </c>
       <c r="G141" s="13" t="s">
         <v>52</v>
@@ -19774,7 +19765,7 @@
       <c r="P141" s="14"/>
       <c r="Q141" s="15"/>
     </row>
-    <row r="142" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="11" t="n">
         <v>141</v>
       </c>
@@ -19782,16 +19773,16 @@
         <v>47</v>
       </c>
       <c r="C142" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D142" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="D142" s="11" t="s">
-        <v>392</v>
-      </c>
       <c r="E142" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G142" s="13" t="s">
         <v>52</v>
@@ -19811,7 +19802,7 @@
       <c r="P142" s="14"/>
       <c r="Q142" s="15"/>
     </row>
-    <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="11" t="n">
         <v>142</v>
       </c>
@@ -19819,27 +19810,29 @@
         <v>55</v>
       </c>
       <c r="C143" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="D143" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="D143" s="12" t="s">
-        <v>394</v>
-      </c>
       <c r="E143" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F143" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G143" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I143" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J143" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J143" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="K143" s="14"/>
       <c r="L143" s="14"/>
       <c r="M143" s="14"/>
@@ -19856,28 +19849,28 @@
         <v>59</v>
       </c>
       <c r="C144" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D144" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="D144" s="11" t="s">
-        <v>396</v>
-      </c>
       <c r="E144" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G144" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J144" s="12" t="s">
-        <v>118</v>
+        <v>296</v>
+      </c>
+      <c r="J144" s="11" t="s">
+        <v>396</v>
       </c>
       <c r="K144" s="14"/>
       <c r="L144" s="14"/>
@@ -19901,22 +19894,22 @@
         <v>398</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G145" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J145" s="11" t="s">
-        <v>399</v>
+        <v>103</v>
+      </c>
+      <c r="J145" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="K145" s="14"/>
       <c r="L145" s="14"/>
@@ -19934,28 +19927,28 @@
         <v>47</v>
       </c>
       <c r="C146" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D146" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="D146" s="11" t="s">
-        <v>401</v>
-      </c>
       <c r="E146" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J146" s="12" t="s">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="K146" s="14"/>
       <c r="L146" s="14"/>
@@ -19973,29 +19966,27 @@
         <v>55</v>
       </c>
       <c r="C147" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D147" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="D147" s="11" t="s">
-        <v>403</v>
-      </c>
       <c r="E147" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F147" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I147" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J147" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I147" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J147" s="11"/>
       <c r="K147" s="14"/>
       <c r="L147" s="14"/>
       <c r="M147" s="14"/>
@@ -20012,27 +20003,29 @@
         <v>59</v>
       </c>
       <c r="C148" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D148" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="D148" s="11" t="s">
-        <v>405</v>
-      </c>
       <c r="E148" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I148" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J148" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>405</v>
+      </c>
       <c r="K148" s="14"/>
       <c r="L148" s="14"/>
       <c r="M148" s="14"/>
@@ -20051,26 +20044,26 @@
       <c r="C149" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="D149" s="12" t="s">
+      <c r="D149" s="11" t="s">
         <v>407</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F149" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G149" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J149" s="12" t="s">
-        <v>408</v>
+        <v>95</v>
       </c>
       <c r="K149" s="14"/>
       <c r="L149" s="14"/>
@@ -20088,29 +20081,27 @@
         <v>47</v>
       </c>
       <c r="C150" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D150" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D150" s="11" t="s">
-        <v>410</v>
-      </c>
       <c r="E150" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F150" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G150" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I150" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J150" s="12" t="s">
-        <v>95</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I150" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J150" s="11"/>
       <c r="K150" s="14"/>
       <c r="L150" s="14"/>
       <c r="M150" s="14"/>
@@ -20119,7 +20110,7 @@
       <c r="P150" s="14"/>
       <c r="Q150" s="15"/>
     </row>
-    <row r="151" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="11" t="n">
         <v>150</v>
       </c>
@@ -20127,22 +20118,22 @@
         <v>55</v>
       </c>
       <c r="C151" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="D151" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="D151" s="12" t="s">
-        <v>412</v>
-      </c>
       <c r="E151" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G151" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I151" s="11" t="s">
         <v>54</v>
@@ -20156,7 +20147,7 @@
       <c r="P151" s="14"/>
       <c r="Q151" s="15"/>
     </row>
-    <row r="152" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="11" t="n">
         <v>151</v>
       </c>
@@ -20164,27 +20155,29 @@
         <v>59</v>
       </c>
       <c r="C152" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="D152" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="D152" s="12" t="s">
-        <v>414</v>
-      </c>
       <c r="E152" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F152" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G152" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I152" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J152" s="11"/>
+        <v>58</v>
+      </c>
+      <c r="I152" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>297</v>
+      </c>
       <c r="K152" s="14"/>
       <c r="L152" s="14"/>
       <c r="M152" s="14"/>
@@ -20193,7 +20186,7 @@
       <c r="P152" s="14"/>
       <c r="Q152" s="15"/>
     </row>
-    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="11" t="n">
         <v>152</v>
       </c>
@@ -20201,16 +20194,16 @@
         <v>63</v>
       </c>
       <c r="C153" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="D153" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="D153" s="11" t="s">
-        <v>416</v>
-      </c>
       <c r="E153" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F153" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G153" s="13" t="s">
         <v>52</v>
@@ -20218,12 +20211,10 @@
       <c r="H153" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I153" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J153" s="11" t="s">
-        <v>300</v>
-      </c>
+      <c r="I153" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J153" s="11"/>
       <c r="K153" s="14"/>
       <c r="L153" s="14"/>
       <c r="M153" s="14"/>
@@ -20232,7 +20223,7 @@
       <c r="P153" s="14"/>
       <c r="Q153" s="15"/>
     </row>
-    <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="11" t="n">
         <v>153</v>
       </c>
@@ -20240,16 +20231,16 @@
         <v>47</v>
       </c>
       <c r="C154" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D154" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="D154" s="11" t="s">
-        <v>418</v>
-      </c>
       <c r="E154" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F154" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G154" s="13" t="s">
         <v>52</v>
@@ -20277,16 +20268,16 @@
         <v>55</v>
       </c>
       <c r="C155" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D155" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D155" s="11" t="s">
-        <v>420</v>
-      </c>
       <c r="E155" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F155" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G155" s="13" t="s">
         <v>52</v>
@@ -20294,10 +20285,12 @@
       <c r="H155" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I155" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J155" s="11"/>
+      <c r="I155" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>420</v>
+      </c>
       <c r="K155" s="14"/>
       <c r="L155" s="14"/>
       <c r="M155" s="14"/>
@@ -20320,10 +20313,10 @@
         <v>422</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F156" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G156" s="13" t="s">
         <v>52</v>
@@ -20331,12 +20324,10 @@
       <c r="H156" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I156" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J156" s="11" t="s">
-        <v>423</v>
-      </c>
+      <c r="I156" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J156" s="11"/>
       <c r="K156" s="14"/>
       <c r="L156" s="14"/>
       <c r="M156" s="14"/>
@@ -20353,27 +20344,29 @@
         <v>63</v>
       </c>
       <c r="C157" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="D157" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="D157" s="11" t="s">
-        <v>425</v>
-      </c>
       <c r="E157" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I157" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J157" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>425</v>
+      </c>
       <c r="K157" s="14"/>
       <c r="L157" s="14"/>
       <c r="M157" s="14"/>
@@ -20392,27 +20385,25 @@
       <c r="C158" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="D158" s="12" t="s">
+      <c r="D158" s="11" t="s">
         <v>427</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F158" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G158" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I158" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J158" s="12" t="s">
-        <v>428</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I158" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J158" s="11"/>
       <c r="K158" s="14"/>
       <c r="L158" s="14"/>
       <c r="M158" s="14"/>
@@ -20429,27 +20420,29 @@
         <v>55</v>
       </c>
       <c r="C159" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D159" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="D159" s="11" t="s">
-        <v>430</v>
-      </c>
       <c r="E159" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F159" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G159" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H159" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I159" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J159" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I159" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J159" s="12" t="s">
+        <v>430</v>
+      </c>
       <c r="K159" s="14"/>
       <c r="L159" s="14"/>
       <c r="M159" s="14"/>
@@ -20468,27 +20461,25 @@
       <c r="C160" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="D160" s="12" t="s">
+      <c r="D160" s="11" t="s">
         <v>432</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G160" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I160" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J160" s="12" t="s">
-        <v>433</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I160" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J160" s="11"/>
       <c r="K160" s="14"/>
       <c r="L160" s="14"/>
       <c r="M160" s="14"/>
@@ -20505,16 +20496,16 @@
         <v>63</v>
       </c>
       <c r="C161" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="D161" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="D161" s="11" t="s">
-        <v>435</v>
-      </c>
       <c r="E161" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F161" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G161" s="13" t="s">
         <v>52</v>
@@ -20522,10 +20513,12 @@
       <c r="H161" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I161" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J161" s="11"/>
+      <c r="I161" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J161" s="11" t="s">
+        <v>297</v>
+      </c>
       <c r="K161" s="14"/>
       <c r="L161" s="14"/>
       <c r="M161" s="14"/>
@@ -20542,28 +20535,28 @@
         <v>47</v>
       </c>
       <c r="C162" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D162" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="D162" s="11" t="s">
-        <v>437</v>
-      </c>
       <c r="E162" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F162" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G162" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J162" s="11" t="s">
-        <v>300</v>
+        <v>94</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>425</v>
       </c>
       <c r="K162" s="14"/>
       <c r="L162" s="14"/>
@@ -20581,28 +20574,28 @@
         <v>55</v>
       </c>
       <c r="C163" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="D163" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="D163" s="11" t="s">
-        <v>439</v>
-      </c>
       <c r="E163" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F163" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G163" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J163" s="12" t="s">
-        <v>428</v>
+        <v>296</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="K163" s="14"/>
       <c r="L163" s="14"/>
@@ -20620,16 +20613,16 @@
         <v>59</v>
       </c>
       <c r="C164" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="D164" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="D164" s="11" t="s">
-        <v>441</v>
-      </c>
       <c r="E164" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F164" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G164" s="13" t="s">
         <v>52</v>
@@ -20638,10 +20631,10 @@
         <v>58</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J164" s="11" t="s">
-        <v>300</v>
+        <v>441</v>
       </c>
       <c r="K164" s="14"/>
       <c r="L164" s="14"/>
@@ -20665,10 +20658,10 @@
         <v>443</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F165" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G165" s="13" t="s">
         <v>52</v>
@@ -20676,12 +20669,10 @@
       <c r="H165" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I165" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J165" s="11" t="s">
-        <v>444</v>
-      </c>
+      <c r="I165" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J165" s="11"/>
       <c r="K165" s="14"/>
       <c r="L165" s="14"/>
       <c r="M165" s="14"/>
@@ -20698,27 +20689,29 @@
         <v>47</v>
       </c>
       <c r="C166" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="D166" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D166" s="11" t="s">
-        <v>446</v>
-      </c>
       <c r="E166" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F166" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G166" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I166" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J166" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I166" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>405</v>
+      </c>
       <c r="K166" s="14"/>
       <c r="L166" s="14"/>
       <c r="M166" s="14"/>
@@ -20735,28 +20728,28 @@
         <v>55</v>
       </c>
       <c r="C167" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="D167" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="D167" s="11" t="s">
-        <v>448</v>
-      </c>
       <c r="E167" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F167" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G167" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>408</v>
+        <v>95</v>
       </c>
       <c r="K167" s="14"/>
       <c r="L167" s="14"/>
@@ -20766,7 +20759,7 @@
       <c r="P167" s="14"/>
       <c r="Q167" s="15"/>
     </row>
-    <row r="168" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="11" t="n">
         <v>167</v>
       </c>
@@ -20774,29 +20767,27 @@
         <v>59</v>
       </c>
       <c r="C168" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="D168" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D168" s="11" t="s">
-        <v>450</v>
-      </c>
       <c r="E168" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F168" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G168" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H168" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I168" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J168" s="12" t="s">
-        <v>95</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I168" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J168" s="11"/>
       <c r="K168" s="14"/>
       <c r="L168" s="14"/>
       <c r="M168" s="14"/>
@@ -20805,7 +20796,7 @@
       <c r="P168" s="14"/>
       <c r="Q168" s="15"/>
     </row>
-    <row r="169" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="11" t="n">
         <v>168</v>
       </c>
@@ -20813,27 +20804,29 @@
         <v>63</v>
       </c>
       <c r="C169" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="D169" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D169" s="11" t="s">
-        <v>452</v>
-      </c>
       <c r="E169" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F169" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G169" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I169" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J169" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="K169" s="14"/>
       <c r="L169" s="14"/>
       <c r="M169" s="14"/>
@@ -20850,16 +20843,16 @@
         <v>47</v>
       </c>
       <c r="C170" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="D170" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="D170" s="11" t="s">
-        <v>454</v>
-      </c>
       <c r="E170" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F170" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G170" s="13" t="s">
         <v>52</v>
@@ -20868,10 +20861,10 @@
         <v>82</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J170" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K170" s="14"/>
       <c r="L170" s="14"/>
@@ -20889,28 +20882,28 @@
         <v>55</v>
       </c>
       <c r="C171" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D171" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="D171" s="11" t="s">
-        <v>456</v>
-      </c>
       <c r="E171" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F171" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G171" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H171" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I171" s="12" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="J171" s="12" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="K171" s="14"/>
       <c r="L171" s="14"/>
@@ -20928,29 +20921,27 @@
         <v>59</v>
       </c>
       <c r="C172" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="D172" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D172" s="12" t="s">
-        <v>458</v>
-      </c>
       <c r="E172" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F172" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G172" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H172" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J172" s="12" t="s">
-        <v>250</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I172" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J172" s="11"/>
       <c r="K172" s="14"/>
       <c r="L172" s="14"/>
       <c r="M172" s="14"/>
@@ -20967,27 +20958,29 @@
         <v>63</v>
       </c>
       <c r="C173" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="D173" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="D173" s="11" t="s">
-        <v>460</v>
-      </c>
       <c r="E173" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F173" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G173" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I173" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J173" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>405</v>
+      </c>
       <c r="K173" s="14"/>
       <c r="L173" s="14"/>
       <c r="M173" s="14"/>
@@ -21004,29 +20997,27 @@
         <v>47</v>
       </c>
       <c r="C174" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="D174" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="D174" s="12" t="s">
-        <v>462</v>
-      </c>
       <c r="E174" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F174" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G174" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H174" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I174" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J174" s="12" t="s">
-        <v>408</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I174" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J174" s="11"/>
       <c r="K174" s="14"/>
       <c r="L174" s="14"/>
       <c r="M174" s="14"/>
@@ -21043,16 +21034,16 @@
         <v>55</v>
       </c>
       <c r="C175" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="D175" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="D175" s="11" t="s">
-        <v>464</v>
-      </c>
       <c r="E175" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F175" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G175" s="13" t="s">
         <v>52</v>
@@ -21080,16 +21071,16 @@
         <v>59</v>
       </c>
       <c r="C176" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="D176" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="D176" s="12" t="s">
-        <v>466</v>
-      </c>
       <c r="E176" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F176" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G176" s="13" t="s">
         <v>52</v>
@@ -21117,27 +21108,29 @@
         <v>63</v>
       </c>
       <c r="C177" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="D177" s="12" t="s">
-        <v>468</v>
-      </c>
       <c r="E177" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F177" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G177" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I177" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J177" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I177" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J177" s="12" t="s">
+        <v>468</v>
+      </c>
       <c r="K177" s="14"/>
       <c r="L177" s="14"/>
       <c r="M177" s="14"/>
@@ -21156,14 +21149,14 @@
       <c r="C178" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="D178" s="11" t="s">
+      <c r="D178" s="12" t="s">
         <v>470</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G178" s="13" t="s">
         <v>52</v>
@@ -21172,10 +21165,10 @@
         <v>102</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>471</v>
+        <v>247</v>
       </c>
       <c r="K178" s="14"/>
       <c r="L178" s="14"/>
@@ -21193,29 +21186,27 @@
         <v>55</v>
       </c>
       <c r="C179" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="D179" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="D179" s="12" t="s">
-        <v>473</v>
-      </c>
       <c r="E179" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G179" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I179" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J179" s="12" t="s">
-        <v>250</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I179" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J179" s="11"/>
       <c r="K179" s="14"/>
       <c r="L179" s="14"/>
       <c r="M179" s="14"/>
@@ -21232,16 +21223,16 @@
         <v>59</v>
       </c>
       <c r="C180" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D180" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="D180" s="11" t="s">
-        <v>475</v>
-      </c>
       <c r="E180" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G180" s="13" t="s">
         <v>52</v>
@@ -21249,10 +21240,12 @@
       <c r="H180" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I180" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J180" s="11"/>
+      <c r="I180" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="J180" s="11" t="s">
+        <v>297</v>
+      </c>
       <c r="K180" s="14"/>
       <c r="L180" s="14"/>
       <c r="M180" s="14"/>
@@ -21269,28 +21262,28 @@
         <v>63</v>
       </c>
       <c r="C181" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D181" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="D181" s="11" t="s">
-        <v>477</v>
-      </c>
       <c r="E181" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F181" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G181" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H181" s="12" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="I181" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J181" s="11" t="s">
-        <v>300</v>
+        <v>108</v>
+      </c>
+      <c r="J181" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="K181" s="14"/>
       <c r="L181" s="14"/>
@@ -21308,28 +21301,28 @@
         <v>47</v>
       </c>
       <c r="C182" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="D182" s="11" t="s">
-        <v>479</v>
-      </c>
       <c r="E182" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G182" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H182" s="12" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I182" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J182" s="12" t="s">
-        <v>109</v>
+        <v>296</v>
+      </c>
+      <c r="J182" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="K182" s="14"/>
       <c r="L182" s="14"/>
@@ -21347,16 +21340,16 @@
         <v>55</v>
       </c>
       <c r="C183" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="D183" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="D183" s="11" t="s">
-        <v>481</v>
-      </c>
       <c r="E183" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G183" s="13" t="s">
         <v>52</v>
@@ -21364,12 +21357,10 @@
       <c r="H183" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I183" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J183" s="11" t="s">
-        <v>300</v>
-      </c>
+      <c r="I183" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J183" s="11"/>
       <c r="K183" s="14"/>
       <c r="L183" s="14"/>
       <c r="M183" s="14"/>
@@ -21386,16 +21377,16 @@
         <v>59</v>
       </c>
       <c r="C184" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="D184" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D184" s="11" t="s">
-        <v>483</v>
-      </c>
       <c r="E184" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G184" s="13" t="s">
         <v>52</v>
@@ -21415,7 +21406,7 @@
       <c r="P184" s="14"/>
       <c r="Q184" s="15"/>
     </row>
-    <row r="185" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="11" t="n">
         <v>184</v>
       </c>
@@ -21423,16 +21414,16 @@
         <v>63</v>
       </c>
       <c r="C185" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="D185" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="D185" s="11" t="s">
-        <v>485</v>
-      </c>
       <c r="E185" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G185" s="13" t="s">
         <v>52</v>
@@ -21440,10 +21431,12 @@
       <c r="H185" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I185" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J185" s="11"/>
+      <c r="I185" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="J185" s="11" t="s">
+        <v>486</v>
+      </c>
       <c r="K185" s="14"/>
       <c r="L185" s="14"/>
       <c r="M185" s="14"/>
@@ -21452,7 +21445,7 @@
       <c r="P185" s="14"/>
       <c r="Q185" s="15"/>
     </row>
-    <row r="186" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="11" t="n">
         <v>185</v>
       </c>
@@ -21460,28 +21453,28 @@
         <v>47</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G186" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H186" s="12" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="J186" s="11" t="s">
-        <v>489</v>
+        <v>94</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>425</v>
       </c>
       <c r="K186" s="14"/>
       <c r="L186" s="14"/>
@@ -21499,16 +21492,16 @@
         <v>55</v>
       </c>
       <c r="C187" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="D187" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="D187" s="11" t="s">
-        <v>491</v>
-      </c>
       <c r="E187" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G187" s="13" t="s">
         <v>52</v>
@@ -21520,7 +21513,7 @@
         <v>94</v>
       </c>
       <c r="J187" s="12" t="s">
-        <v>428</v>
+        <v>118</v>
       </c>
       <c r="K187" s="14"/>
       <c r="L187" s="14"/>
@@ -21538,28 +21531,28 @@
         <v>59</v>
       </c>
       <c r="C188" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="D188" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="D188" s="11" t="s">
-        <v>493</v>
-      </c>
       <c r="E188" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G188" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H188" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>94</v>
+        <v>493</v>
       </c>
       <c r="J188" s="12" t="s">
-        <v>118</v>
+        <v>494</v>
       </c>
       <c r="K188" s="14"/>
       <c r="L188" s="14"/>
@@ -21577,28 +21570,28 @@
         <v>63</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="D189" s="11" t="s">
         <v>495</v>
       </c>
+      <c r="D189" s="12" t="s">
+        <v>496</v>
+      </c>
       <c r="E189" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G189" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H189" s="12" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>496</v>
+        <v>103</v>
       </c>
       <c r="J189" s="12" t="s">
-        <v>497</v>
+        <v>247</v>
       </c>
       <c r="K189" s="14"/>
       <c r="L189" s="14"/>
@@ -21616,28 +21609,28 @@
         <v>47</v>
       </c>
       <c r="C190" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="D190" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="D190" s="12" t="s">
-        <v>499</v>
-      </c>
       <c r="E190" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F190" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G190" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H190" s="12" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J190" s="12" t="s">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="K190" s="14"/>
       <c r="L190" s="14"/>
@@ -21655,16 +21648,16 @@
         <v>55</v>
       </c>
       <c r="C191" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="D191" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="D191" s="12" t="s">
-        <v>501</v>
-      </c>
       <c r="E191" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F191" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G191" s="13" t="s">
         <v>52</v>
@@ -21676,7 +21669,7 @@
         <v>94</v>
       </c>
       <c r="J191" s="12" t="s">
-        <v>118</v>
+        <v>425</v>
       </c>
       <c r="K191" s="14"/>
       <c r="L191" s="14"/>
@@ -21686,7 +21679,7 @@
       <c r="P191" s="14"/>
       <c r="Q191" s="15"/>
     </row>
-    <row r="192" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="11" t="n">
         <v>191</v>
       </c>
@@ -21694,28 +21687,28 @@
         <v>59</v>
       </c>
       <c r="C192" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="D192" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D192" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="E192" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F192" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G192" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H192" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J192" s="12" t="s">
-        <v>428</v>
+        <v>296</v>
+      </c>
+      <c r="J192" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="K192" s="14"/>
       <c r="L192" s="14"/>
@@ -21725,7 +21718,7 @@
       <c r="P192" s="14"/>
       <c r="Q192" s="15"/>
     </row>
-    <row r="193" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="11" t="n">
         <v>192</v>
       </c>
@@ -21733,16 +21726,16 @@
         <v>63</v>
       </c>
       <c r="C193" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="D193" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="D193" s="11" t="s">
-        <v>505</v>
-      </c>
       <c r="E193" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F193" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G193" s="13" t="s">
         <v>52</v>
@@ -21751,10 +21744,10 @@
         <v>58</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J193" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K193" s="14"/>
       <c r="L193" s="14"/>
@@ -21764,7 +21757,7 @@
       <c r="P193" s="14"/>
       <c r="Q193" s="15"/>
     </row>
-    <row r="194" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="11" t="n">
         <v>193</v>
       </c>
@@ -21772,16 +21765,16 @@
         <v>47</v>
       </c>
       <c r="C194" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="D194" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="D194" s="11" t="s">
-        <v>507</v>
-      </c>
       <c r="E194" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G194" s="13" t="s">
         <v>52</v>
@@ -21790,10 +21783,10 @@
         <v>58</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J194" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K194" s="14"/>
       <c r="L194" s="14"/>
@@ -21803,7 +21796,7 @@
       <c r="P194" s="14"/>
       <c r="Q194" s="15"/>
     </row>
-    <row r="195" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="11" t="n">
         <v>194</v>
       </c>
@@ -21811,16 +21804,16 @@
         <v>55</v>
       </c>
       <c r="C195" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="D195" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="D195" s="11" t="s">
-        <v>509</v>
-      </c>
       <c r="E195" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G195" s="13" t="s">
         <v>52</v>
@@ -21828,12 +21821,10 @@
       <c r="H195" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I195" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="J195" s="11" t="s">
-        <v>300</v>
-      </c>
+      <c r="I195" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J195" s="11"/>
       <c r="K195" s="14"/>
       <c r="L195" s="14"/>
       <c r="M195" s="14"/>
@@ -21850,16 +21841,16 @@
         <v>59</v>
       </c>
       <c r="C196" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="D196" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="D196" s="11" t="s">
-        <v>511</v>
-      </c>
       <c r="E196" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G196" s="13" t="s">
         <v>52</v>
@@ -21887,27 +21878,29 @@
         <v>63</v>
       </c>
       <c r="C197" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="D197" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="D197" s="12" t="s">
-        <v>513</v>
-      </c>
       <c r="E197" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G197" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H197" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I197" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J197" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J197" s="12" t="s">
+        <v>425</v>
+      </c>
       <c r="K197" s="14"/>
       <c r="L197" s="14"/>
       <c r="M197" s="14"/>
@@ -21924,29 +21917,27 @@
         <v>47</v>
       </c>
       <c r="C198" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="D198" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="D198" s="11" t="s">
-        <v>515</v>
-      </c>
       <c r="E198" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F198" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G198" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H198" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I198" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J198" s="12" t="s">
-        <v>428</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I198" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J198" s="11"/>
       <c r="K198" s="14"/>
       <c r="L198" s="14"/>
       <c r="M198" s="14"/>
@@ -21955,7 +21946,7 @@
       <c r="P198" s="14"/>
       <c r="Q198" s="15"/>
     </row>
-    <row r="199" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="11" t="n">
         <v>198</v>
       </c>
@@ -21963,16 +21954,16 @@
         <v>55</v>
       </c>
       <c r="C199" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="D199" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="D199" s="11" t="s">
-        <v>517</v>
-      </c>
       <c r="E199" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F199" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G199" s="13" t="s">
         <v>52</v>
@@ -21992,7 +21983,7 @@
       <c r="P199" s="14"/>
       <c r="Q199" s="15"/>
     </row>
-    <row r="200" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="11" t="n">
         <v>199</v>
       </c>
@@ -22000,27 +21991,29 @@
         <v>59</v>
       </c>
       <c r="C200" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D200" s="11" t="s">
-        <v>519</v>
-      </c>
       <c r="E200" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G200" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H200" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I200" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J200" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="K200" s="14"/>
       <c r="L200" s="14"/>
       <c r="M200" s="14"/>
@@ -22037,29 +22030,27 @@
         <v>63</v>
       </c>
       <c r="C201" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="D201" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="D201" s="11" t="s">
-        <v>521</v>
-      </c>
       <c r="E201" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G201" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H201" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I201" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J201" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I201" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J201" s="11"/>
       <c r="K201" s="14"/>
       <c r="L201" s="14"/>
       <c r="M201" s="14"/>
@@ -22068,7 +22059,7 @@
       <c r="P201" s="14"/>
       <c r="Q201" s="15"/>
     </row>
-    <row r="202" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="11" t="n">
         <v>201</v>
       </c>
@@ -22076,16 +22067,16 @@
         <v>47</v>
       </c>
       <c r="C202" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="D202" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="D202" s="12" t="s">
+      <c r="E202" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="E202" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="F202" s="12" t="s">
-        <v>390</v>
+        <v>523</v>
       </c>
       <c r="G202" s="13" t="s">
         <v>52</v>
@@ -22105,7 +22096,7 @@
       <c r="P202" s="14"/>
       <c r="Q202" s="15"/>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="11" t="n">
         <v>202</v>
       </c>
@@ -22119,10 +22110,10 @@
         <v>525</v>
       </c>
       <c r="E203" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G203" s="13" t="s">
         <v>52</v>
@@ -22142,7 +22133,7 @@
       <c r="P203" s="14"/>
       <c r="Q203" s="15"/>
     </row>
-    <row r="204" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="11" t="n">
         <v>203</v>
       </c>
@@ -22150,16 +22141,16 @@
         <v>59</v>
       </c>
       <c r="C204" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="D204" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="D204" s="11" t="s">
-        <v>528</v>
-      </c>
       <c r="E204" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G204" s="13" t="s">
         <v>52</v>
@@ -22187,27 +22178,29 @@
         <v>63</v>
       </c>
       <c r="C205" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="D205" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="D205" s="12" t="s">
-        <v>530</v>
-      </c>
       <c r="E205" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F205" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G205" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H205" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I205" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J205" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="K205" s="14"/>
       <c r="L205" s="14"/>
       <c r="M205" s="14"/>
@@ -22224,16 +22217,16 @@
         <v>47</v>
       </c>
       <c r="C206" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="D206" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="D206" s="11" t="s">
-        <v>532</v>
-      </c>
       <c r="E206" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F206" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G206" s="13" t="s">
         <v>52</v>
@@ -22242,10 +22235,10 @@
         <v>82</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J206" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K206" s="14"/>
       <c r="L206" s="14"/>
@@ -22263,16 +22256,16 @@
         <v>55</v>
       </c>
       <c r="C207" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="D207" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="D207" s="11" t="s">
-        <v>534</v>
-      </c>
       <c r="E207" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G207" s="13" t="s">
         <v>52</v>
@@ -22281,10 +22274,10 @@
         <v>82</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J207" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K207" s="14"/>
       <c r="L207" s="14"/>
@@ -22294,7 +22287,7 @@
       <c r="P207" s="14"/>
       <c r="Q207" s="15"/>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="11" t="n">
         <v>207</v>
       </c>
@@ -22302,28 +22295,28 @@
         <v>59</v>
       </c>
       <c r="C208" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="D208" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="D208" s="11" t="s">
-        <v>536</v>
-      </c>
       <c r="E208" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F208" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G208" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H208" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="J208" s="12" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="K208" s="14"/>
       <c r="L208" s="14"/>
@@ -22333,7 +22326,7 @@
       <c r="P208" s="14"/>
       <c r="Q208" s="15"/>
     </row>
-    <row r="209" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="11" t="n">
         <v>208</v>
       </c>
@@ -22341,16 +22334,16 @@
         <v>63</v>
       </c>
       <c r="C209" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="D209" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="D209" s="11" t="s">
-        <v>538</v>
-      </c>
       <c r="E209" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F209" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G209" s="13" t="s">
         <v>52</v>
@@ -22362,7 +22355,7 @@
         <v>103</v>
       </c>
       <c r="J209" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K209" s="14"/>
       <c r="L209" s="14"/>
@@ -22372,7 +22365,7 @@
       <c r="P209" s="14"/>
       <c r="Q209" s="15"/>
     </row>
-    <row r="210" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="11" t="n">
         <v>209</v>
       </c>
@@ -22380,29 +22373,27 @@
         <v>47</v>
       </c>
       <c r="C210" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="D210" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="D210" s="12" t="s">
-        <v>540</v>
-      </c>
       <c r="E210" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F210" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G210" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H210" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I210" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J210" s="12" t="s">
-        <v>250</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I210" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J210" s="11"/>
       <c r="K210" s="14"/>
       <c r="L210" s="14"/>
       <c r="M210" s="14"/>
@@ -22419,16 +22410,16 @@
         <v>55</v>
       </c>
       <c r="C211" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="D211" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="D211" s="12" t="s">
-        <v>542</v>
-      </c>
       <c r="E211" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F211" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G211" s="13" t="s">
         <v>52</v>
@@ -22456,27 +22447,29 @@
         <v>59</v>
       </c>
       <c r="C212" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="D212" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="D212" s="11" t="s">
-        <v>544</v>
-      </c>
       <c r="E212" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F212" s="12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G212" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H212" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I212" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J212" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>247</v>
+      </c>
       <c r="K212" s="14"/>
       <c r="L212" s="14"/>
       <c r="M212" s="14"/>
@@ -22485,66 +22478,27 @@
       <c r="P212" s="14"/>
       <c r="Q212" s="15"/>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="11" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C213" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="D213" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="E213" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="F213" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="G213" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H213" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I213" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J213" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="K213" s="14"/>
-      <c r="L213" s="14"/>
-      <c r="M213" s="14"/>
-      <c r="N213" s="14"/>
-      <c r="O213" s="14"/>
-      <c r="P213" s="14"/>
-      <c r="Q213" s="15"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q213"/>
-  <conditionalFormatting sqref="L2:L213">
+  <autoFilter ref="A1:Q212"/>
+  <conditionalFormatting sqref="L2:L212">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>AND(OR(L2="틀림",L2="일부 틀림"),M2="",N2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" error="관련 / 일부 관련 / 무관 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K213" type="list">
+    <dataValidation allowBlank="true" error="관련 / 일부 관련 / 무관 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K212" type="list">
       <formula1>"관련,일부 관련,무관"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="맞음 / 일부 틀림 / 틀림 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L213" type="list">
+    <dataValidation allowBlank="true" error="맞음 / 일부 틀림 / 틀림 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L212" type="list">
       <formula1>"맞음,일부 틀림,틀림"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="팀원A~D 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P2:P213" type="list">
+    <dataValidation allowBlank="true" error="팀원A~D 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P2:P212" type="list">
       <formula1>"팀원A,팀원B,팀원C,팀원D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="날짜(예: 2026-10-30)를 입력하세요" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q213" type="date">
+    <dataValidation allowBlank="true" error="날짜(예: 2026-10-30)를 입력하세요" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q212" type="date">
       <formula1>DATE(2026,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -22761,7 +22715,6 @@
     <hyperlink ref="G210" r:id="rId210" display="열기"/>
     <hyperlink ref="G211" r:id="rId211" display="열기"/>
     <hyperlink ref="G212" r:id="rId212" display="열기"/>
-    <hyperlink ref="G213" r:id="rId213" display="열기"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22770,8 +22723,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId214"/>
-  <legacyDrawing r:id="rId215"/>
+  <drawing r:id="rId213"/>
+  <legacyDrawing r:id="rId214"/>
 </worksheet>
 </file>
 
@@ -22806,7 +22759,7 @@
         <v>37</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>38</v>
@@ -22848,19 +22801,19 @@
         <v>46</v>
       </c>
       <c r="P1" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="S1" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="T1" s="10" t="s">
         <v>549</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22897,11 +22850,11 @@
         <v>47</v>
       </c>
       <c r="Q2" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C2,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C2,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C2,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C2,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R2" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C2,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C2,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C2,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C2,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S2" s="11" t="str">
@@ -22949,11 +22902,11 @@
         <v>63</v>
       </c>
       <c r="Q3" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C3,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C3,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C3,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C3,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R3" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C3,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C3,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C3,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C3,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S3" s="11" t="str">
@@ -23001,11 +22954,11 @@
         <v>47</v>
       </c>
       <c r="Q4" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C4,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C4,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C4,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C4,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R4" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C4,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C4,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C4,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C4,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S4" s="11" t="str">
@@ -23053,11 +23006,11 @@
         <v>59</v>
       </c>
       <c r="Q5" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C5,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C5,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C5,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C5,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R5" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C5,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C5,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C5,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C5,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S5" s="11" t="str">
@@ -23074,16 +23027,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>52</v>
@@ -23102,14 +23055,14 @@
       <c r="N6" s="14"/>
       <c r="O6" s="15"/>
       <c r="P6" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q6" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C6,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C6,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C6,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C6,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R6" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C6,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C6,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C6,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C6,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S6" s="11" t="str">
@@ -23126,16 +23079,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>52</v>
@@ -23152,14 +23105,14 @@
       <c r="N7" s="14"/>
       <c r="O7" s="15"/>
       <c r="P7" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C7,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C7,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C7,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C7,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R7" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C7,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C7,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C7,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C7,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S7" s="11" t="str">
@@ -23176,25 +23129,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -23204,14 +23157,14 @@
       <c r="N8" s="14"/>
       <c r="O8" s="15"/>
       <c r="P8" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C8,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C8,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C8,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C8,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R8" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C8,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C8,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C8,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C8,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S8" s="11" t="str">
@@ -23228,13 +23181,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>74</v>
@@ -23256,14 +23209,14 @@
       <c r="N9" s="14"/>
       <c r="O9" s="15"/>
       <c r="P9" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C9,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C9,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C9,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C9,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R9" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C9,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C9,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C9,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C9,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S9" s="11" t="str">
@@ -23280,13 +23233,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>74</v>
@@ -23308,14 +23261,14 @@
       <c r="N10" s="14"/>
       <c r="O10" s="15"/>
       <c r="P10" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q10" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C10,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C10,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C10,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C10,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R10" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C10,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C10,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C10,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C10,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S10" s="11" t="str">
@@ -23332,13 +23285,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>74</v>
@@ -23347,10 +23300,10 @@
         <v>52</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
@@ -23360,14 +23313,14 @@
       <c r="N11" s="14"/>
       <c r="O11" s="15"/>
       <c r="P11" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q11" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C11,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C11,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C11,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C11,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R11" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C11,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C11,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C11,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C11,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S11" s="11" t="str">
@@ -23387,10 +23340,10 @@
         <v>59</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>74</v>
@@ -23402,7 +23355,7 @@
         <v>103</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
@@ -23412,14 +23365,14 @@
       <c r="N12" s="14"/>
       <c r="O12" s="15"/>
       <c r="P12" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q12" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C12,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C12,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C12,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C12,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R12" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C12,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C12,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C12,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C12,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S12" s="11" t="str">
@@ -23436,13 +23389,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>74</v>
@@ -23451,10 +23404,10 @@
         <v>52</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -23464,14 +23417,14 @@
       <c r="N13" s="14"/>
       <c r="O13" s="15"/>
       <c r="P13" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C13,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C13,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C13,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C13,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R13" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C13,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C13,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C13,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C13,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S13" s="11" t="str">
@@ -23488,25 +23441,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
@@ -23516,14 +23469,14 @@
       <c r="N14" s="14"/>
       <c r="O14" s="15"/>
       <c r="P14" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q14" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C14,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C14,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C14,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C14,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R14" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C14,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C14,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C14,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C14,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S14" s="11" t="str">
@@ -23543,22 +23496,22 @@
         <v>55</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -23568,14 +23521,14 @@
       <c r="N15" s="14"/>
       <c r="O15" s="15"/>
       <c r="P15" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C15,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C15,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C15,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C15,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R15" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C15,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C15,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C15,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C15,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S15" s="11" t="str">
@@ -23592,16 +23545,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>52</v>
@@ -23610,7 +23563,7 @@
         <v>94</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -23620,14 +23573,14 @@
       <c r="N16" s="14"/>
       <c r="O16" s="15"/>
       <c r="P16" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q16" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C16,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C16,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C16,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C16,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R16" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C16,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C16,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C16,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C16,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S16" s="11" t="str">
@@ -23644,16 +23597,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>52</v>
@@ -23662,7 +23615,7 @@
         <v>103</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -23672,14 +23625,14 @@
       <c r="N17" s="14"/>
       <c r="O17" s="15"/>
       <c r="P17" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q17" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C17,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C17,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C17,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C17,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R17" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C17,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C17,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C17,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C17,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S17" s="11" t="str">
@@ -23696,25 +23649,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
@@ -23724,14 +23677,14 @@
       <c r="N18" s="14"/>
       <c r="O18" s="15"/>
       <c r="P18" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q18" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C18,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C18,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C18,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C18,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R18" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C18,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C18,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C18,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C18,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S18" s="11" t="str">
@@ -23751,13 +23704,13 @@
         <v>55</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>52</v>
@@ -23766,7 +23719,7 @@
         <v>33</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
@@ -23776,14 +23729,14 @@
       <c r="N19" s="14"/>
       <c r="O19" s="15"/>
       <c r="P19" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q19" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C19,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C19,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C19,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C19,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R19" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C19,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C19,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C19,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C19,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S19" s="11" t="str">
@@ -23803,22 +23756,22 @@
         <v>59</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
@@ -23828,14 +23781,14 @@
       <c r="N20" s="14"/>
       <c r="O20" s="15"/>
       <c r="P20" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q20" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C20,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C20,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C20,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C20,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R20" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C20,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C20,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C20,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C20,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S20" s="11" t="str">
@@ -23852,25 +23805,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
@@ -23880,14 +23833,14 @@
       <c r="N21" s="14"/>
       <c r="O21" s="15"/>
       <c r="P21" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="Q21" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$213,MATCH($C21,검수!$C$2:$C$213,0))="","",INDEX(검수!$K$2:$K$213,MATCH($C21,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C21,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C21,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="R21" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$213,MATCH($C21,검수!$C$2:$C$213,0))="","",INDEX(검수!$L$2:$L$213,MATCH($C21,검수!$C$2:$C$213,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C21,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C21,검수!$C$2:$C$212,0))),"")</f>
         <v/>
       </c>
       <c r="S21" s="11" t="str">
@@ -23966,30 +23919,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B3" s="19" t="n">
-        <f aca="false">COUNTA(검수!$C$2:$C$213)</f>
-        <v>212</v>
+        <f aca="false">COUNTA(검수!$C$2:$C$212)</f>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B4" s="19" t="n">
-        <f aca="false">COUNTA(검수!$L$2:$L$213)</f>
+        <f aca="false">COUNTA(검수!$L$2:$L$212)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B5" s="20" t="n">
         <f aca="false">IF(B3=0,0,B4/B3)</f>
@@ -24001,18 +23954,18 @@
         <v>30</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B8" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$L$2:$L$213,A8)</f>
+        <f aca="false">COUNTIF(검수!$L$2:$L$212,A8)</f>
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
@@ -24025,7 +23978,7 @@
         <v>31</v>
       </c>
       <c r="B9" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$L$2:$L$213,A9)</f>
+        <f aca="false">COUNTIF(검수!$L$2:$L$212,A9)</f>
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
@@ -24035,10 +23988,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B10" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$L$2:$L$213,A10)</f>
+        <f aca="false">COUNTIF(검수!$L$2:$L$212,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
@@ -24051,7 +24004,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24059,59 +24012,59 @@
         <v>29</v>
       </c>
       <c r="B13" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$K$2:$K$213,A13)</f>
+        <f aca="false">COUNTIF(검수!$K$2:$K$212,A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B14" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$K$2:$K$213,A14)</f>
+        <f aca="false">COUNTIF(검수!$K$2:$K$212,A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B15" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$K$2:$K$213,A15)</f>
+        <f aca="false">COUNTIF(검수!$K$2:$K$212,A15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
+        <v>560</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>563</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>564</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>565</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>559</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B18" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A18&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A18&amp;"*")</f>
         <v>1</v>
       </c>
       <c r="C18" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A18&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A18&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D18" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A18&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A18&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E18" s="20" t="n">
@@ -24121,18 +24074,18 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B19" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A19&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A19&amp;"*")</f>
         <v>1</v>
       </c>
       <c r="C19" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A19&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A19&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D19" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A19&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A19&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E19" s="20" t="n">
@@ -24145,15 +24098,15 @@
         <v>108</v>
       </c>
       <c r="B20" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A20&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A20&amp;"*")</f>
         <v>48</v>
       </c>
       <c r="C20" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A20&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A20&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D20" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A20&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A20&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E20" s="20" t="n">
@@ -24163,18 +24116,18 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B21" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A21&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A21&amp;"*")</f>
         <v>12</v>
       </c>
       <c r="C21" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A21&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A21&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D21" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A21&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A21&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E21" s="20" t="n">
@@ -24187,15 +24140,15 @@
         <v>103</v>
       </c>
       <c r="B22" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A22&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A22&amp;"*")</f>
         <v>21</v>
       </c>
       <c r="C22" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A22&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A22&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D22" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A22&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A22&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E22" s="20" t="n">
@@ -24208,15 +24161,15 @@
         <v>33</v>
       </c>
       <c r="B23" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A23&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A23&amp;"*")</f>
         <v>2</v>
       </c>
       <c r="C23" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A23&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A23&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D23" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A23&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A23&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E23" s="20" t="n">
@@ -24226,18 +24179,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B24" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A24&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A24&amp;"*")</f>
         <v>18</v>
       </c>
       <c r="C24" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A24&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A24&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D24" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A24&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A24&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E24" s="20" t="n">
@@ -24247,18 +24200,18 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B25" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A25&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A25&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="C25" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A25&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A25&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D25" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A25&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A25&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E25" s="20" t="n">
@@ -24271,15 +24224,15 @@
         <v>94</v>
       </c>
       <c r="B26" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"*"&amp;A26&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A26&amp;"*")</f>
         <v>26</v>
       </c>
       <c r="C26" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A26&amp;"*",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A26&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D26" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"*"&amp;A26&amp;"*",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A26&amp;"*",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E26" s="20" t="n">
@@ -24292,15 +24245,15 @@
         <v>54</v>
       </c>
       <c r="B27" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$213,"(없음)")</f>
-        <v>88</v>
+        <f aca="false">COUNTIF(검수!$I$2:$I$212,"(없음)")</f>
+        <v>87</v>
       </c>
       <c r="C27" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"(없음)",검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"(없음)",검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D27" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$213,"(없음)",검수!$L$2:$L$213,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"(없음)",검수!$L$2:$L$212,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E27" s="20" t="n">
@@ -24310,27 +24263,27 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24338,11 +24291,11 @@
         <v>47</v>
       </c>
       <c r="B31" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$213,A31)</f>
+        <f aca="false">COUNTIF(검수!$B$2:$B$212,A31)</f>
         <v>53</v>
       </c>
       <c r="C31" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$213,A31,검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A31,검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D31" s="20" t="n">
@@ -24363,11 +24316,11 @@
         <v>55</v>
       </c>
       <c r="B32" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$213,A32)</f>
+        <f aca="false">COUNTIF(검수!$B$2:$B$212,A32)</f>
         <v>53</v>
       </c>
       <c r="C32" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$213,A32,검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A32,검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D32" s="20" t="n">
@@ -24388,11 +24341,11 @@
         <v>59</v>
       </c>
       <c r="B33" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$213,A33)</f>
+        <f aca="false">COUNTIF(검수!$B$2:$B$212,A33)</f>
         <v>53</v>
       </c>
       <c r="C33" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$213,A33,검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A33,검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D33" s="20" t="n">
@@ -24413,11 +24366,11 @@
         <v>63</v>
       </c>
       <c r="B34" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$213,A34)</f>
-        <v>53</v>
+        <f aca="false">COUNTIF(검수!$B$2:$B$212,A34)</f>
+        <v>52</v>
       </c>
       <c r="C34" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$213,A34,검수!$L$2:$L$213,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A34,검수!$L$2:$L$212,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D34" s="20" t="n">
@@ -24435,12 +24388,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B38" s="21" t="n">
         <f aca="false">COUNTA(교차검수!$C$2:$C$21)</f>
@@ -24449,7 +24402,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B39" s="21" t="n">
         <f aca="false">SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;"")))</f>
@@ -24458,7 +24411,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B40" s="21" t="n">
         <f aca="false">SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21=교차검수!$J$2:$J$21))</f>
@@ -24467,7 +24420,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B41" s="20" t="n">
         <f aca="false">IF(B39=0,0,B40/B39)</f>
@@ -24476,7 +24429,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">IF(B39=0,0,(SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21="맞음"))*SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$J$2:$J$21="맞음"))+SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21="일부 틀림"))*SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$J$2:$J$21="일부 틀림"))+SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21="틀림"))*SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$J$2:$J$21="틀림")))/B39^2)</f>
@@ -24485,7 +24438,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B43" s="24" t="str">
         <f aca="false">IF(OR(B39=0,B42=1),"-",(B41-B42)/(1-B42))</f>
@@ -24494,7 +24447,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B44" s="20" t="n">
         <f aca="false">IF(SUMPRODUCT((교차검수!$Q$2:$Q$21&lt;&gt;"")*(교차검수!$I$2:$I$21&lt;&gt;""))=0,0,SUMPRODUCT((교차검수!$Q$2:$Q$21&lt;&gt;"")*(교차검수!$I$2:$I$21&lt;&gt;"")*(교차검수!$Q$2:$Q$21=교차검수!$I$2:$I$21))/SUMPRODUCT((교차검수!$Q$2:$Q$21&lt;&gt;"")*(교차검수!$I$2:$I$21&lt;&gt;"")))</f>
@@ -24503,7 +24456,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -24532,112 +24485,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>94</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/data/hr/output/recommendation/domain_mapping_review_sheet.xlsx
+++ b/data/hr/output/recommendation/domain_mapping_review_sheet.xlsx
@@ -15,7 +15,7 @@
     <sheet name="분야 기준" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">검수!$A$1:$Q$212</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">검수!$A$1:$Q$184</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">교차검수!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="543">
   <si>
     <t xml:space="preserve">분야–과정 연결 검수 시트</t>
   </si>
@@ -3819,1945 +3819,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">보고법</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370512</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보건업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370513</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기타사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370514</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370515</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건설업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370516</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제조업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370517</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유통업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370518</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370519</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보건업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370520</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기타사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370521</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370522</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일반근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건설업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370555</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370556</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건설업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370477</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제조업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370478</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유통업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370479</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370480</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보건업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370481</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기타사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370482</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">금융업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370483</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리감독자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건설업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370509</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제조업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370510</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유통업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370511</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 일용 및 초단기 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370550</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제조업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370551</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유통업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370552</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">서비스업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370553</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보건업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL_HUNET_Y00370554</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">안전보건교육 기간제근로자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채용 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기타사업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -14350,7 +12411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q212"/>
+  <dimension ref="A1:Q184"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -16167,7 +14228,7 @@
       <c r="P47" s="14"/>
       <c r="Q47" s="15"/>
     </row>
-    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
@@ -16190,14 +14251,12 @@
         <v>52</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J48" s="11"/>
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
@@ -16206,7 +14265,7 @@
       <c r="P48" s="14"/>
       <c r="Q48" s="15"/>
     </row>
-    <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="n">
         <v>48</v>
       </c>
@@ -16229,13 +14288,13 @@
         <v>52</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
@@ -16245,7 +14304,7 @@
       <c r="P49" s="14"/>
       <c r="Q49" s="15"/>
     </row>
-    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="n">
         <v>49</v>
       </c>
@@ -16253,10 +14312,10 @@
         <v>47</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>74</v>
@@ -16271,10 +14330,10 @@
         <v>82</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
@@ -16284,7 +14343,7 @@
       <c r="P50" s="14"/>
       <c r="Q50" s="15"/>
     </row>
-    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="n">
         <v>50</v>
       </c>
@@ -16292,10 +14351,10 @@
         <v>55</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D51" s="11" t="s">
         <v>194</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>74</v>
@@ -16307,14 +14366,12 @@
         <v>52</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I51" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J51" s="11"/>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
@@ -16331,10 +14388,10 @@
         <v>59</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>74</v>
@@ -16346,13 +14403,13 @@
         <v>52</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>
@@ -16370,10 +14427,10 @@
         <v>63</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D53" s="11" t="s">
         <v>198</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>74</v>
@@ -16385,13 +14442,13 @@
         <v>52</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
@@ -16409,10 +14466,10 @@
         <v>47</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D54" s="11" t="s">
         <v>200</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>74</v>
@@ -16424,13 +14481,13 @@
         <v>52</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
@@ -16448,10 +14505,10 @@
         <v>55</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D55" s="11" t="s">
         <v>202</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>74</v>
@@ -16487,10 +14544,10 @@
         <v>59</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="D56" s="11" t="s">
         <v>204</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>74</v>
@@ -16508,7 +14565,7 @@
         <v>108</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
@@ -16526,10 +14583,10 @@
         <v>63</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>74</v>
@@ -16541,13 +14598,13 @@
         <v>52</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
@@ -16565,10 +14622,10 @@
         <v>47</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>74</v>
@@ -16580,14 +14637,12 @@
         <v>52</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J58" s="11"/>
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
@@ -16596,7 +14651,7 @@
       <c r="P58" s="14"/>
       <c r="Q58" s="15"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="n">
         <v>58</v>
       </c>
@@ -16604,10 +14659,10 @@
         <v>55</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>74</v>
@@ -16619,14 +14674,12 @@
         <v>52</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J59" s="11"/>
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
@@ -16643,10 +14696,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>214</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>74</v>
@@ -16658,14 +14711,12 @@
         <v>52</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J60" s="11"/>
       <c r="K60" s="14"/>
       <c r="L60" s="14"/>
       <c r="M60" s="14"/>
@@ -16682,10 +14733,10 @@
         <v>63</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>74</v>
@@ -16703,7 +14754,7 @@
         <v>108</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="K61" s="14"/>
       <c r="L61" s="14"/>
@@ -16721,10 +14772,10 @@
         <v>47</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>74</v>
@@ -16742,7 +14793,7 @@
         <v>108</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="K62" s="14"/>
       <c r="L62" s="14"/>
@@ -16760,10 +14811,10 @@
         <v>55</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>74</v>
@@ -16799,10 +14850,10 @@
         <v>59</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>74</v>
@@ -16817,10 +14868,10 @@
         <v>82</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
@@ -16838,10 +14889,10 @@
         <v>63</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E65" s="12" t="s">
         <v>74</v>
@@ -16859,7 +14910,7 @@
         <v>108</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
@@ -16877,10 +14928,10 @@
         <v>47</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>74</v>
@@ -16895,10 +14946,10 @@
         <v>82</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
@@ -16908,7 +14959,7 @@
       <c r="P66" s="14"/>
       <c r="Q66" s="15"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="n">
         <v>66</v>
       </c>
@@ -16916,10 +14967,10 @@
         <v>55</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>74</v>
@@ -16931,13 +14982,13 @@
         <v>52</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="K67" s="14"/>
       <c r="L67" s="14"/>
@@ -16955,10 +15006,10 @@
         <v>59</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>74</v>
@@ -16970,14 +15021,12 @@
         <v>52</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J68" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J68" s="11"/>
       <c r="K68" s="14"/>
       <c r="L68" s="14"/>
       <c r="M68" s="14"/>
@@ -16994,10 +15043,10 @@
         <v>63</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>74</v>
@@ -17009,14 +15058,12 @@
         <v>52</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I69" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J69" s="11"/>
       <c r="K69" s="14"/>
       <c r="L69" s="14"/>
       <c r="M69" s="14"/>
@@ -17033,10 +15080,10 @@
         <v>47</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>74</v>
@@ -17048,14 +15095,12 @@
         <v>52</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J70" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J70" s="11"/>
       <c r="K70" s="14"/>
       <c r="L70" s="14"/>
       <c r="M70" s="14"/>
@@ -17072,10 +15117,10 @@
         <v>55</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>74</v>
@@ -17087,14 +15132,12 @@
         <v>52</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J71" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J71" s="11"/>
       <c r="K71" s="14"/>
       <c r="L71" s="14"/>
       <c r="M71" s="14"/>
@@ -17111,10 +15154,10 @@
         <v>59</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>74</v>
@@ -17126,13 +15169,13 @@
         <v>52</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>109</v>
+        <v>240</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="K72" s="14"/>
       <c r="L72" s="14"/>
@@ -17142,7 +15185,7 @@
       <c r="P72" s="14"/>
       <c r="Q72" s="15"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="n">
         <v>72</v>
       </c>
@@ -17150,10 +15193,10 @@
         <v>63</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>74</v>
@@ -17165,14 +15208,12 @@
         <v>52</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J73" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J73" s="11"/>
       <c r="K73" s="14"/>
       <c r="L73" s="14"/>
       <c r="M73" s="14"/>
@@ -17189,28 +15230,28 @@
         <v>47</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>108</v>
+        <v>240</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="K74" s="14"/>
       <c r="L74" s="14"/>
@@ -17220,7 +15261,7 @@
       <c r="P74" s="14"/>
       <c r="Q74" s="15"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="n">
         <v>74</v>
       </c>
@@ -17228,28 +15269,28 @@
         <v>55</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J75" s="12" t="s">
-        <v>109</v>
+        <v>240</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="K75" s="14"/>
       <c r="L75" s="14"/>
@@ -17259,7 +15300,7 @@
       <c r="P75" s="14"/>
       <c r="Q75" s="15"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="n">
         <v>75</v>
       </c>
@@ -17267,16 +15308,16 @@
         <v>59</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>52</v>
@@ -17284,10 +15325,12 @@
       <c r="H76" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I76" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J76" s="11"/>
+      <c r="I76" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
       <c r="M76" s="14"/>
@@ -17304,16 +15347,16 @@
         <v>63</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D77" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="E77" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="E77" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="F77" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>52</v>
@@ -17325,7 +15368,7 @@
         <v>103</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="K77" s="14"/>
       <c r="L77" s="14"/>
@@ -17335,7 +15378,7 @@
       <c r="P77" s="14"/>
       <c r="Q77" s="15"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="n">
         <v>77</v>
       </c>
@@ -17343,28 +15386,28 @@
         <v>47</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="K78" s="14"/>
       <c r="L78" s="14"/>
@@ -17382,27 +15425,29 @@
         <v>55</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>251</v>
+        <v>257</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>258</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I79" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J79" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="K79" s="14"/>
       <c r="L79" s="14"/>
       <c r="M79" s="14"/>
@@ -17411,7 +15456,7 @@
       <c r="P79" s="14"/>
       <c r="Q79" s="15"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="11" t="n">
         <v>79</v>
       </c>
@@ -17419,29 +15464,27 @@
         <v>59</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I80" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J80" s="12" t="s">
-        <v>247</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J80" s="11"/>
       <c r="K80" s="14"/>
       <c r="L80" s="14"/>
       <c r="M80" s="14"/>
@@ -17450,7 +15493,7 @@
       <c r="P80" s="14"/>
       <c r="Q80" s="15"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="n">
         <v>80</v>
       </c>
@@ -17458,29 +15501,27 @@
         <v>63</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>255</v>
+        <v>261</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>262</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J81" s="12" t="s">
-        <v>247</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J81" s="11"/>
       <c r="K81" s="14"/>
       <c r="L81" s="14"/>
       <c r="M81" s="14"/>
@@ -17497,29 +15538,27 @@
         <v>47</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>257</v>
+        <v>263</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>264</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J82" s="12" t="s">
-        <v>247</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J82" s="11"/>
       <c r="K82" s="14"/>
       <c r="L82" s="14"/>
       <c r="M82" s="14"/>
@@ -17528,7 +15567,7 @@
       <c r="P82" s="14"/>
       <c r="Q82" s="15"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="n">
         <v>82</v>
       </c>
@@ -17536,29 +15575,27 @@
         <v>55</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>259</v>
+        <v>265</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>266</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I83" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J83" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J83" s="11"/>
       <c r="K83" s="14"/>
       <c r="L83" s="14"/>
       <c r="M83" s="14"/>
@@ -17575,29 +15612,27 @@
         <v>59</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>261</v>
+        <v>267</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>268</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J84" s="12" t="s">
-        <v>262</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J84" s="11"/>
       <c r="K84" s="14"/>
       <c r="L84" s="14"/>
       <c r="M84" s="14"/>
@@ -17606,7 +15641,7 @@
       <c r="P84" s="14"/>
       <c r="Q84" s="15"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="n">
         <v>84</v>
       </c>
@@ -17614,29 +15649,27 @@
         <v>63</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>264</v>
+        <v>269</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I85" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J85" s="12" t="s">
-        <v>247</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J85" s="11"/>
       <c r="K85" s="14"/>
       <c r="L85" s="14"/>
       <c r="M85" s="14"/>
@@ -17653,16 +15686,16 @@
         <v>47</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>52</v>
@@ -17682,7 +15715,7 @@
       <c r="P86" s="14"/>
       <c r="Q86" s="15"/>
     </row>
-    <row r="87" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="n">
         <v>86</v>
       </c>
@@ -17690,16 +15723,16 @@
         <v>55</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>52</v>
@@ -17719,7 +15752,7 @@
       <c r="P87" s="14"/>
       <c r="Q87" s="15"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="n">
         <v>87</v>
       </c>
@@ -17727,16 +15760,16 @@
         <v>59</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>276</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>52</v>
@@ -17764,29 +15797,27 @@
         <v>63</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>278</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J89" s="12" t="s">
-        <v>162</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J89" s="11"/>
       <c r="K89" s="14"/>
       <c r="L89" s="14"/>
       <c r="M89" s="14"/>
@@ -17795,7 +15826,7 @@
       <c r="P89" s="14"/>
       <c r="Q89" s="15"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="n">
         <v>89</v>
       </c>
@@ -17803,29 +15834,27 @@
         <v>47</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I90" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J90" s="12" t="s">
-        <v>162</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I90" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J90" s="11"/>
       <c r="K90" s="14"/>
       <c r="L90" s="14"/>
       <c r="M90" s="14"/>
@@ -17842,29 +15871,27 @@
         <v>55</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>276</v>
+        <v>281</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>282</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I91" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J91" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J91" s="11"/>
       <c r="K91" s="14"/>
       <c r="L91" s="14"/>
       <c r="M91" s="14"/>
@@ -17873,7 +15900,7 @@
       <c r="P91" s="14"/>
       <c r="Q91" s="15"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="n">
         <v>91</v>
       </c>
@@ -17881,29 +15908,27 @@
         <v>59</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>278</v>
+        <v>283</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>284</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J92" s="12" t="s">
-        <v>168</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J92" s="11"/>
       <c r="K92" s="14"/>
       <c r="L92" s="14"/>
       <c r="M92" s="14"/>
@@ -17912,7 +15937,7 @@
       <c r="P92" s="14"/>
       <c r="Q92" s="15"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="11" t="n">
         <v>92</v>
       </c>
@@ -17920,29 +15945,27 @@
         <v>63</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I93" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J93" s="12" t="s">
-        <v>162</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J93" s="11"/>
       <c r="K93" s="14"/>
       <c r="L93" s="14"/>
       <c r="M93" s="14"/>
@@ -17951,7 +15974,7 @@
       <c r="P93" s="14"/>
       <c r="Q93" s="15"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="11" t="n">
         <v>93</v>
       </c>
@@ -17959,29 +15982,27 @@
         <v>47</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I94" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J94" s="12" t="s">
-        <v>168</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J94" s="11"/>
       <c r="K94" s="14"/>
       <c r="L94" s="14"/>
       <c r="M94" s="14"/>
@@ -17998,29 +16019,27 @@
         <v>55</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I95" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J95" s="12" t="s">
-        <v>285</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I95" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J95" s="11"/>
       <c r="K95" s="14"/>
       <c r="L95" s="14"/>
       <c r="M95" s="14"/>
@@ -18037,16 +16056,16 @@
         <v>59</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>52</v>
@@ -18074,22 +16093,22 @@
         <v>63</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>289</v>
+        <v>293</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>294</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>54</v>
@@ -18111,16 +16130,16 @@
         <v>47</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>52</v>
@@ -18148,16 +16167,16 @@
         <v>55</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>52</v>
@@ -18177,7 +16196,7 @@
       <c r="P99" s="14"/>
       <c r="Q99" s="15"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="11" t="n">
         <v>99</v>
       </c>
@@ -18185,16 +16204,16 @@
         <v>59</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G100" s="13" t="s">
         <v>52</v>
@@ -18202,12 +16221,10 @@
       <c r="H100" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I100" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>297</v>
-      </c>
+      <c r="I100" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J100" s="11"/>
       <c r="K100" s="14"/>
       <c r="L100" s="14"/>
       <c r="M100" s="14"/>
@@ -18216,7 +16233,7 @@
       <c r="P100" s="14"/>
       <c r="Q100" s="15"/>
     </row>
-    <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="n">
         <v>100</v>
       </c>
@@ -18224,27 +16241,29 @@
         <v>63</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="G101" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I101" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J101" s="11"/>
+        <v>58</v>
+      </c>
+      <c r="I101" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="K101" s="14"/>
       <c r="L101" s="14"/>
       <c r="M101" s="14"/>
@@ -18253,7 +16272,7 @@
       <c r="P101" s="14"/>
       <c r="Q101" s="15"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="11" t="n">
         <v>101</v>
       </c>
@@ -18261,16 +16280,16 @@
         <v>47</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>52</v>
@@ -18279,10 +16298,10 @@
         <v>58</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J102" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>306</v>
       </c>
       <c r="K102" s="14"/>
       <c r="L102" s="14"/>
@@ -18300,28 +16319,28 @@
         <v>55</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J103" s="11" t="s">
-        <v>297</v>
+        <v>94</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>309</v>
       </c>
       <c r="K103" s="14"/>
       <c r="L103" s="14"/>
@@ -18331,7 +16350,7 @@
       <c r="P103" s="14"/>
       <c r="Q103" s="15"/>
     </row>
-    <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="11" t="n">
         <v>103</v>
       </c>
@@ -18339,28 +16358,28 @@
         <v>59</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>297</v>
+        <v>108</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="K104" s="14"/>
       <c r="L104" s="14"/>
@@ -18378,28 +16397,28 @@
         <v>63</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G105" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>247</v>
+        <v>109</v>
       </c>
       <c r="K105" s="14"/>
       <c r="L105" s="14"/>
@@ -18409,7 +16428,7 @@
       <c r="P105" s="14"/>
       <c r="Q105" s="15"/>
     </row>
-    <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="11" t="n">
         <v>105</v>
       </c>
@@ -18417,28 +16436,28 @@
         <v>47</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G106" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
       <c r="K106" s="14"/>
       <c r="L106" s="14"/>
@@ -18448,7 +16467,7 @@
       <c r="P106" s="14"/>
       <c r="Q106" s="15"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="11" t="n">
         <v>106</v>
       </c>
@@ -18456,28 +16475,28 @@
         <v>55</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G107" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H107" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="K107" s="14"/>
       <c r="L107" s="14"/>
@@ -18487,7 +16506,7 @@
       <c r="P107" s="14"/>
       <c r="Q107" s="15"/>
     </row>
-    <row r="108" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="n">
         <v>107</v>
       </c>
@@ -18495,27 +16514,29 @@
         <v>59</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G108" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I108" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J108" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>309</v>
+      </c>
       <c r="K108" s="14"/>
       <c r="L108" s="14"/>
       <c r="M108" s="14"/>
@@ -18524,7 +16545,7 @@
       <c r="P108" s="14"/>
       <c r="Q108" s="15"/>
     </row>
-    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="n">
         <v>108</v>
       </c>
@@ -18532,27 +16553,29 @@
         <v>63</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G109" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I109" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J109" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>316</v>
+      </c>
       <c r="K109" s="14"/>
       <c r="L109" s="14"/>
       <c r="M109" s="14"/>
@@ -18569,27 +16592,29 @@
         <v>47</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G110" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I110" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J110" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J110" s="12" t="s">
+        <v>316</v>
+      </c>
       <c r="K110" s="14"/>
       <c r="L110" s="14"/>
       <c r="M110" s="14"/>
@@ -18606,16 +16631,16 @@
         <v>55</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="G111" s="13" t="s">
         <v>52</v>
@@ -18635,7 +16660,7 @@
       <c r="P111" s="14"/>
       <c r="Q111" s="15"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="11" t="n">
         <v>111</v>
       </c>
@@ -18643,16 +16668,16 @@
         <v>59</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>329</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G112" s="13" t="s">
         <v>52</v>
@@ -18672,7 +16697,7 @@
       <c r="P112" s="14"/>
       <c r="Q112" s="15"/>
     </row>
-    <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="n">
         <v>112</v>
       </c>
@@ -18680,16 +16705,16 @@
         <v>63</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>52</v>
@@ -18709,7 +16734,7 @@
       <c r="P113" s="14"/>
       <c r="Q113" s="15"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="11" t="n">
         <v>113</v>
       </c>
@@ -18717,16 +16742,16 @@
         <v>47</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>328</v>
+        <v>334</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G114" s="13" t="s">
         <v>52</v>
@@ -18746,7 +16771,7 @@
       <c r="P114" s="14"/>
       <c r="Q114" s="15"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="11" t="n">
         <v>114</v>
       </c>
@@ -18754,27 +16779,29 @@
         <v>55</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D115" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="E115" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="E115" s="12" t="s">
-        <v>302</v>
-      </c>
       <c r="F115" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G115" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I115" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J115" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="K115" s="14"/>
       <c r="L115" s="14"/>
       <c r="M115" s="14"/>
@@ -18783,7 +16810,7 @@
       <c r="P115" s="14"/>
       <c r="Q115" s="15"/>
     </row>
-    <row r="116" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="11" t="n">
         <v>115</v>
       </c>
@@ -18791,16 +16818,16 @@
         <v>59</v>
       </c>
       <c r="C116" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="F116" s="12" t="s">
         <v>331</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="E116" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="F116" s="12" t="s">
-        <v>303</v>
       </c>
       <c r="G116" s="13" t="s">
         <v>52</v>
@@ -18808,10 +16835,12 @@
       <c r="H116" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I116" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J116" s="11"/>
+      <c r="I116" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>340</v>
+      </c>
       <c r="K116" s="14"/>
       <c r="L116" s="14"/>
       <c r="M116" s="14"/>
@@ -18820,7 +16849,7 @@
       <c r="P116" s="14"/>
       <c r="Q116" s="15"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="11" t="n">
         <v>116</v>
       </c>
@@ -18828,27 +16857,29 @@
         <v>63</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G117" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I117" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J117" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J117" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="K117" s="14"/>
       <c r="L117" s="14"/>
       <c r="M117" s="14"/>
@@ -18857,7 +16888,7 @@
       <c r="P117" s="14"/>
       <c r="Q117" s="15"/>
     </row>
-    <row r="118" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="11" t="n">
         <v>117</v>
       </c>
@@ -18865,27 +16896,29 @@
         <v>47</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G118" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I118" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J118" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J118" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="K118" s="14"/>
       <c r="L118" s="14"/>
       <c r="M118" s="14"/>
@@ -18894,7 +16927,7 @@
       <c r="P118" s="14"/>
       <c r="Q118" s="15"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="11" t="n">
         <v>118</v>
       </c>
@@ -18902,16 +16935,16 @@
         <v>55</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G119" s="13" t="s">
         <v>52</v>
@@ -18939,27 +16972,29 @@
         <v>59</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>340</v>
+        <v>347</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F120" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G120" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I120" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J120" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J120" s="12" t="s">
+        <v>349</v>
+      </c>
       <c r="K120" s="14"/>
       <c r="L120" s="14"/>
       <c r="M120" s="14"/>
@@ -18968,7 +17003,7 @@
       <c r="P120" s="14"/>
       <c r="Q120" s="15"/>
     </row>
-    <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="11" t="n">
         <v>120</v>
       </c>
@@ -18976,27 +17011,29 @@
         <v>63</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G121" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I121" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J121" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J121" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="K121" s="14"/>
       <c r="L121" s="14"/>
       <c r="M121" s="14"/>
@@ -19005,7 +17042,7 @@
       <c r="P121" s="14"/>
       <c r="Q121" s="15"/>
     </row>
-    <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="11" t="n">
         <v>121</v>
       </c>
@@ -19013,16 +17050,16 @@
         <v>47</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>344</v>
+        <v>352</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>353</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F122" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G122" s="13" t="s">
         <v>52</v>
@@ -19050,22 +17087,22 @@
         <v>55</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>346</v>
+        <v>354</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F123" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G123" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I123" s="11" t="s">
         <v>54</v>
@@ -19079,7 +17116,7 @@
       <c r="P123" s="14"/>
       <c r="Q123" s="15"/>
     </row>
-    <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="11" t="n">
         <v>123</v>
       </c>
@@ -19087,16 +17124,16 @@
         <v>59</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F124" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G124" s="13" t="s">
         <v>52</v>
@@ -19104,10 +17141,12 @@
       <c r="H124" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I124" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J124" s="11"/>
+      <c r="I124" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="K124" s="14"/>
       <c r="L124" s="14"/>
       <c r="M124" s="14"/>
@@ -19124,16 +17163,16 @@
         <v>63</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G125" s="13" t="s">
         <v>52</v>
@@ -19153,7 +17192,7 @@
       <c r="P125" s="14"/>
       <c r="Q125" s="15"/>
     </row>
-    <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="11" t="n">
         <v>125</v>
       </c>
@@ -19161,16 +17200,16 @@
         <v>47</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G126" s="13" t="s">
         <v>52</v>
@@ -19190,7 +17229,7 @@
       <c r="P126" s="14"/>
       <c r="Q126" s="15"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="11" t="n">
         <v>126</v>
       </c>
@@ -19198,16 +17237,16 @@
         <v>55</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F127" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G127" s="13" t="s">
         <v>52</v>
@@ -19215,10 +17254,12 @@
       <c r="H127" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I127" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J127" s="11"/>
+      <c r="I127" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>364</v>
+      </c>
       <c r="K127" s="14"/>
       <c r="L127" s="14"/>
       <c r="M127" s="14"/>
@@ -19227,7 +17268,7 @@
       <c r="P127" s="14"/>
       <c r="Q127" s="15"/>
     </row>
-    <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="11" t="n">
         <v>127</v>
       </c>
@@ -19235,16 +17276,16 @@
         <v>59</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G128" s="13" t="s">
         <v>52</v>
@@ -19264,7 +17305,7 @@
       <c r="P128" s="14"/>
       <c r="Q128" s="15"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="11" t="n">
         <v>128</v>
       </c>
@@ -19272,28 +17313,28 @@
         <v>63</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="D129" s="11" t="s">
-        <v>358</v>
+        <v>367</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G129" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I129" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>297</v>
+        <v>94</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>369</v>
       </c>
       <c r="K129" s="14"/>
       <c r="L129" s="14"/>
@@ -19303,7 +17344,7 @@
       <c r="P129" s="14"/>
       <c r="Q129" s="15"/>
     </row>
-    <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="11" t="n">
         <v>129</v>
       </c>
@@ -19311,16 +17352,16 @@
         <v>47</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G130" s="13" t="s">
         <v>52</v>
@@ -19328,12 +17369,10 @@
       <c r="H130" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I130" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="J130" s="11" t="s">
-        <v>362</v>
-      </c>
+      <c r="I130" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J130" s="11"/>
       <c r="K130" s="14"/>
       <c r="L130" s="14"/>
       <c r="M130" s="14"/>
@@ -19342,7 +17381,7 @@
       <c r="P130" s="14"/>
       <c r="Q130" s="15"/>
     </row>
-    <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="11" t="n">
         <v>130</v>
       </c>
@@ -19350,28 +17389,28 @@
         <v>55</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="D131" s="11" t="s">
-        <v>364</v>
+        <v>372</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G131" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="K131" s="14"/>
       <c r="L131" s="14"/>
@@ -19381,7 +17420,7 @@
       <c r="P131" s="14"/>
       <c r="Q131" s="15"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="11" t="n">
         <v>131</v>
       </c>
@@ -19389,29 +17428,27 @@
         <v>59</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G132" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I132" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J132" s="12" t="s">
-        <v>162</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I132" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J132" s="11"/>
       <c r="K132" s="14"/>
       <c r="L132" s="14"/>
       <c r="M132" s="14"/>
@@ -19420,7 +17457,7 @@
       <c r="P132" s="14"/>
       <c r="Q132" s="15"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="11" t="n">
         <v>132</v>
       </c>
@@ -19428,28 +17465,28 @@
         <v>63</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G133" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J133" s="12" t="s">
-        <v>109</v>
+        <v>240</v>
+      </c>
+      <c r="J133" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="K133" s="14"/>
       <c r="L133" s="14"/>
@@ -19459,7 +17496,7 @@
       <c r="P133" s="14"/>
       <c r="Q133" s="15"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="11" t="n">
         <v>133</v>
       </c>
@@ -19467,28 +17504,28 @@
         <v>47</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G134" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K134" s="14"/>
       <c r="L134" s="14"/>
@@ -19498,7 +17535,7 @@
       <c r="P134" s="14"/>
       <c r="Q134" s="15"/>
     </row>
-    <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="11" t="n">
         <v>134</v>
       </c>
@@ -19506,28 +17543,28 @@
         <v>55</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G135" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H135" s="12" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J135" s="12" t="s">
-        <v>375</v>
+        <v>240</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="K135" s="14"/>
       <c r="L135" s="14"/>
@@ -19537,7 +17574,7 @@
       <c r="P135" s="14"/>
       <c r="Q135" s="15"/>
     </row>
-    <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="11" t="n">
         <v>135</v>
       </c>
@@ -19545,28 +17582,28 @@
         <v>59</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G136" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J136" s="12" t="s">
-        <v>365</v>
+        <v>240</v>
+      </c>
+      <c r="J136" s="11" t="s">
+        <v>385</v>
       </c>
       <c r="K136" s="14"/>
       <c r="L136" s="14"/>
@@ -19576,7 +17613,7 @@
       <c r="P136" s="14"/>
       <c r="Q136" s="15"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="11" t="n">
         <v>136</v>
       </c>
@@ -19584,29 +17621,27 @@
         <v>63</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G137" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I137" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J137" s="12" t="s">
-        <v>372</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I137" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J137" s="11"/>
       <c r="K137" s="14"/>
       <c r="L137" s="14"/>
       <c r="M137" s="14"/>
@@ -19615,7 +17650,7 @@
       <c r="P137" s="14"/>
       <c r="Q137" s="15"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="11" t="n">
         <v>137</v>
       </c>
@@ -19623,28 +17658,28 @@
         <v>47</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F138" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G138" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="K138" s="14"/>
       <c r="L138" s="14"/>
@@ -19654,7 +17689,7 @@
       <c r="P138" s="14"/>
       <c r="Q138" s="15"/>
     </row>
-    <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="11" t="n">
         <v>138</v>
       </c>
@@ -19662,27 +17697,29 @@
         <v>55</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F139" s="12" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G139" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I139" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J139" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I139" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J139" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="K139" s="14"/>
       <c r="L139" s="14"/>
       <c r="M139" s="14"/>
@@ -19691,7 +17728,7 @@
       <c r="P139" s="14"/>
       <c r="Q139" s="15"/>
     </row>
-    <row r="140" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="11" t="n">
         <v>139</v>
       </c>
@@ -19699,16 +17736,16 @@
         <v>59</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="D140" s="12" t="s">
-        <v>385</v>
+        <v>392</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>393</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F140" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G140" s="13" t="s">
         <v>52</v>
@@ -19736,27 +17773,29 @@
         <v>63</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F141" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G141" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I141" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J141" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J141" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="K141" s="14"/>
       <c r="L141" s="14"/>
       <c r="M141" s="14"/>
@@ -19765,7 +17804,7 @@
       <c r="P141" s="14"/>
       <c r="Q141" s="15"/>
     </row>
-    <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="11" t="n">
         <v>141</v>
       </c>
@@ -19773,27 +17812,29 @@
         <v>47</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D142" s="12" t="s">
-        <v>391</v>
+        <v>396</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>397</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G142" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I142" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J142" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J142" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="K142" s="14"/>
       <c r="L142" s="14"/>
       <c r="M142" s="14"/>
@@ -19810,28 +17851,28 @@
         <v>55</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="D143" s="11" t="s">
-        <v>393</v>
+        <v>398</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>399</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F143" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G143" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J143" s="12" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="K143" s="14"/>
       <c r="L143" s="14"/>
@@ -19849,16 +17890,16 @@
         <v>59</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G144" s="13" t="s">
         <v>52</v>
@@ -19866,12 +17907,10 @@
       <c r="H144" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I144" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J144" s="11" t="s">
-        <v>396</v>
-      </c>
+      <c r="I144" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J144" s="11"/>
       <c r="K144" s="14"/>
       <c r="L144" s="14"/>
       <c r="M144" s="14"/>
@@ -19888,16 +17927,16 @@
         <v>63</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D145" s="11" t="s">
-        <v>398</v>
+        <v>402</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>403</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G145" s="13" t="s">
         <v>52</v>
@@ -19909,7 +17948,7 @@
         <v>103</v>
       </c>
       <c r="J145" s="12" t="s">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="K145" s="14"/>
       <c r="L145" s="14"/>
@@ -19927,29 +17966,27 @@
         <v>47</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I146" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J146" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I146" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J146" s="11"/>
       <c r="K146" s="14"/>
       <c r="L146" s="14"/>
       <c r="M146" s="14"/>
@@ -19966,16 +18003,16 @@
         <v>55</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="D147" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>407</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F147" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>52</v>
@@ -20003,29 +18040,27 @@
         <v>59</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I148" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J148" s="12" t="s">
-        <v>405</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I148" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J148" s="11"/>
       <c r="K148" s="14"/>
       <c r="L148" s="14"/>
       <c r="M148" s="14"/>
@@ -20042,28 +18077,28 @@
         <v>63</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F149" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G149" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="J149" s="12" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="K149" s="14"/>
       <c r="L149" s="14"/>
@@ -20081,27 +18116,29 @@
         <v>47</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F150" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G150" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I150" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J150" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="K150" s="14"/>
       <c r="L150" s="14"/>
       <c r="M150" s="14"/>
@@ -20110,7 +18147,7 @@
       <c r="P150" s="14"/>
       <c r="Q150" s="15"/>
     </row>
-    <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="11" t="n">
         <v>150</v>
       </c>
@@ -20118,22 +18155,22 @@
         <v>55</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="D151" s="12" t="s">
-        <v>411</v>
+        <v>415</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>416</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G151" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I151" s="11" t="s">
         <v>54</v>
@@ -20155,16 +18192,16 @@
         <v>59</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F152" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G152" s="13" t="s">
         <v>52</v>
@@ -20173,10 +18210,10 @@
         <v>58</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="J152" s="11" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="K152" s="14"/>
       <c r="L152" s="14"/>
@@ -20186,7 +18223,7 @@
       <c r="P152" s="14"/>
       <c r="Q152" s="15"/>
     </row>
-    <row r="153" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="11" t="n">
         <v>152</v>
       </c>
@@ -20194,27 +18231,29 @@
         <v>63</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F153" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G153" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I153" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J153" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I153" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J153" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="K153" s="14"/>
       <c r="L153" s="14"/>
       <c r="M153" s="14"/>
@@ -20231,16 +18270,16 @@
         <v>47</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F154" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G154" s="13" t="s">
         <v>52</v>
@@ -20248,10 +18287,12 @@
       <c r="H154" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I154" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J154" s="11"/>
+      <c r="I154" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J154" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="K154" s="14"/>
       <c r="L154" s="14"/>
       <c r="M154" s="14"/>
@@ -20268,16 +18309,16 @@
         <v>55</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F155" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G155" s="13" t="s">
         <v>52</v>
@@ -20285,12 +18326,10 @@
       <c r="H155" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I155" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J155" s="11" t="s">
-        <v>420</v>
-      </c>
+      <c r="I155" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J155" s="11"/>
       <c r="K155" s="14"/>
       <c r="L155" s="14"/>
       <c r="M155" s="14"/>
@@ -20307,16 +18346,16 @@
         <v>59</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F156" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G156" s="13" t="s">
         <v>52</v>
@@ -20336,7 +18375,7 @@
       <c r="P156" s="14"/>
       <c r="Q156" s="15"/>
     </row>
-    <row r="157" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="11" t="n">
         <v>156</v>
       </c>
@@ -20344,28 +18383,28 @@
         <v>63</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>424</v>
+        <v>427</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>428</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H157" s="12" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J157" s="12" t="s">
-        <v>425</v>
+        <v>429</v>
+      </c>
+      <c r="J157" s="11" t="s">
+        <v>430</v>
       </c>
       <c r="K157" s="14"/>
       <c r="L157" s="14"/>
@@ -20383,27 +18422,29 @@
         <v>47</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F158" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G158" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I158" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J158" s="11"/>
+        <v>89</v>
+      </c>
+      <c r="I158" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>369</v>
+      </c>
       <c r="K158" s="14"/>
       <c r="L158" s="14"/>
       <c r="M158" s="14"/>
@@ -20420,28 +18461,28 @@
         <v>55</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>429</v>
+        <v>433</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>434</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F159" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G159" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H159" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J159" s="12" t="s">
-        <v>430</v>
+        <v>118</v>
       </c>
       <c r="K159" s="14"/>
       <c r="L159" s="14"/>
@@ -20459,16 +18500,16 @@
         <v>59</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G160" s="13" t="s">
         <v>52</v>
@@ -20476,10 +18517,12 @@
       <c r="H160" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I160" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J160" s="11"/>
+      <c r="I160" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>438</v>
+      </c>
       <c r="K160" s="14"/>
       <c r="L160" s="14"/>
       <c r="M160" s="14"/>
@@ -20496,28 +18539,28 @@
         <v>63</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>434</v>
+        <v>439</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>440</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F161" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G161" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J161" s="11" t="s">
-        <v>297</v>
+        <v>103</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="K161" s="14"/>
       <c r="L161" s="14"/>
@@ -20535,16 +18578,16 @@
         <v>47</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="D162" s="11" t="s">
-        <v>436</v>
+        <v>441</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>442</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F162" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G162" s="13" t="s">
         <v>52</v>
@@ -20556,7 +18599,7 @@
         <v>94</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>425</v>
+        <v>118</v>
       </c>
       <c r="K162" s="14"/>
       <c r="L162" s="14"/>
@@ -20574,28 +18617,28 @@
         <v>55</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F163" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G163" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J163" s="11" t="s">
-        <v>297</v>
+        <v>94</v>
+      </c>
+      <c r="J163" s="12" t="s">
+        <v>369</v>
       </c>
       <c r="K163" s="14"/>
       <c r="L163" s="14"/>
@@ -20605,7 +18648,7 @@
       <c r="P163" s="14"/>
       <c r="Q163" s="15"/>
     </row>
-    <row r="164" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="11" t="n">
         <v>163</v>
       </c>
@@ -20613,16 +18656,16 @@
         <v>59</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F164" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G164" s="13" t="s">
         <v>52</v>
@@ -20631,10 +18674,10 @@
         <v>58</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="J164" s="11" t="s">
-        <v>441</v>
+        <v>241</v>
       </c>
       <c r="K164" s="14"/>
       <c r="L164" s="14"/>
@@ -20652,16 +18695,16 @@
         <v>63</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F165" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G165" s="13" t="s">
         <v>52</v>
@@ -20669,10 +18712,12 @@
       <c r="H165" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I165" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J165" s="11"/>
+      <c r="I165" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J165" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="K165" s="14"/>
       <c r="L165" s="14"/>
       <c r="M165" s="14"/>
@@ -20681,7 +18726,7 @@
       <c r="P165" s="14"/>
       <c r="Q165" s="15"/>
     </row>
-    <row r="166" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="11" t="n">
         <v>165</v>
       </c>
@@ -20689,28 +18734,28 @@
         <v>47</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F166" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G166" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J166" s="12" t="s">
-        <v>405</v>
+        <v>240</v>
+      </c>
+      <c r="J166" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="K166" s="14"/>
       <c r="L166" s="14"/>
@@ -20728,29 +18773,27 @@
         <v>55</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F167" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G167" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I167" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J167" s="12" t="s">
-        <v>95</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I167" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J167" s="11"/>
       <c r="K167" s="14"/>
       <c r="L167" s="14"/>
       <c r="M167" s="14"/>
@@ -20759,7 +18802,7 @@
       <c r="P167" s="14"/>
       <c r="Q167" s="15"/>
     </row>
-    <row r="168" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="11" t="n">
         <v>167</v>
       </c>
@@ -20767,16 +18810,16 @@
         <v>59</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>448</v>
-      </c>
-      <c r="D168" s="11" t="s">
-        <v>449</v>
+        <v>453</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>454</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F168" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G168" s="13" t="s">
         <v>52</v>
@@ -20804,28 +18847,28 @@
         <v>63</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F169" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G169" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H169" s="12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>178</v>
+        <v>369</v>
       </c>
       <c r="K169" s="14"/>
       <c r="L169" s="14"/>
@@ -20843,29 +18886,27 @@
         <v>47</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F170" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G170" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H170" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I170" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J170" s="12" t="s">
-        <v>178</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I170" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J170" s="11"/>
       <c r="K170" s="14"/>
       <c r="L170" s="14"/>
       <c r="M170" s="14"/>
@@ -20874,7 +18915,7 @@
       <c r="P170" s="14"/>
       <c r="Q170" s="15"/>
     </row>
-    <row r="171" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="11" t="n">
         <v>170</v>
       </c>
@@ -20882,29 +18923,27 @@
         <v>55</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>455</v>
+        <v>459</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>460</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F171" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G171" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H171" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I171" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J171" s="12" t="s">
-        <v>247</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I171" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J171" s="11"/>
       <c r="K171" s="14"/>
       <c r="L171" s="14"/>
       <c r="M171" s="14"/>
@@ -20921,27 +18960,29 @@
         <v>59</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F172" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G172" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H172" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I172" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J172" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="K172" s="14"/>
       <c r="L172" s="14"/>
       <c r="M172" s="14"/>
@@ -20958,29 +18999,27 @@
         <v>63</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F173" s="12" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="G173" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H173" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I173" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J173" s="12" t="s">
-        <v>405</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I173" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J173" s="11"/>
       <c r="K173" s="14"/>
       <c r="L173" s="14"/>
       <c r="M173" s="14"/>
@@ -20989,7 +19028,7 @@
       <c r="P173" s="14"/>
       <c r="Q173" s="15"/>
     </row>
-    <row r="174" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="11" t="n">
         <v>173</v>
       </c>
@@ -20997,16 +19036,16 @@
         <v>47</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F174" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G174" s="13" t="s">
         <v>52</v>
@@ -21026,7 +19065,7 @@
       <c r="P174" s="14"/>
       <c r="Q174" s="15"/>
     </row>
-    <row r="175" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="11" t="n">
         <v>174</v>
       </c>
@@ -21034,16 +19073,16 @@
         <v>55</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="D175" s="12" t="s">
-        <v>463</v>
+        <v>468</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>469</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F175" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G175" s="13" t="s">
         <v>52</v>
@@ -21063,7 +19102,7 @@
       <c r="P175" s="14"/>
       <c r="Q175" s="15"/>
     </row>
-    <row r="176" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="11" t="n">
         <v>175</v>
       </c>
@@ -21071,16 +19110,16 @@
         <v>59</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F176" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G176" s="13" t="s">
         <v>52</v>
@@ -21100,7 +19139,7 @@
       <c r="P176" s="14"/>
       <c r="Q176" s="15"/>
     </row>
-    <row r="177" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="11" t="n">
         <v>176</v>
       </c>
@@ -21108,28 +19147,28 @@
         <v>63</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D177" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E177" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="E177" s="12" t="s">
-        <v>386</v>
-      </c>
       <c r="F177" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G177" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I177" s="12" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>468</v>
+        <v>178</v>
       </c>
       <c r="K177" s="14"/>
       <c r="L177" s="14"/>
@@ -21139,7 +19178,7 @@
       <c r="P177" s="14"/>
       <c r="Q177" s="15"/>
     </row>
-    <row r="178" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="11" t="n">
         <v>177</v>
       </c>
@@ -21147,28 +19186,28 @@
         <v>47</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>470</v>
+        <v>474</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>475</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G178" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H178" s="12" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>247</v>
+        <v>178</v>
       </c>
       <c r="K178" s="14"/>
       <c r="L178" s="14"/>
@@ -21178,7 +19217,7 @@
       <c r="P178" s="14"/>
       <c r="Q178" s="15"/>
     </row>
-    <row r="179" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="11" t="n">
         <v>178</v>
       </c>
@@ -21186,27 +19225,29 @@
         <v>55</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G179" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I179" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J179" s="11"/>
+        <v>82</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="K179" s="14"/>
       <c r="L179" s="14"/>
       <c r="M179" s="14"/>
@@ -21215,7 +19256,7 @@
       <c r="P179" s="14"/>
       <c r="Q179" s="15"/>
     </row>
-    <row r="180" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="11" t="n">
         <v>179</v>
       </c>
@@ -21223,28 +19264,28 @@
         <v>59</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G180" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J180" s="11" t="s">
-        <v>297</v>
+        <v>103</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="K180" s="14"/>
       <c r="L180" s="14"/>
@@ -21254,7 +19295,7 @@
       <c r="P180" s="14"/>
       <c r="Q180" s="15"/>
     </row>
-    <row r="181" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="11" t="n">
         <v>180</v>
       </c>
@@ -21262,28 +19303,28 @@
         <v>63</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="D181" s="11" t="s">
-        <v>476</v>
+        <v>480</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>481</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F181" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G181" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H181" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I181" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J181" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="K181" s="14"/>
       <c r="L181" s="14"/>
@@ -21293,7 +19334,7 @@
       <c r="P181" s="14"/>
       <c r="Q181" s="15"/>
     </row>
-    <row r="182" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="11" t="n">
         <v>181</v>
       </c>
@@ -21301,16 +19342,16 @@
         <v>47</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="D182" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>483</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G182" s="13" t="s">
         <v>52</v>
@@ -21318,12 +19359,10 @@
       <c r="H182" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I182" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J182" s="11" t="s">
-        <v>297</v>
-      </c>
+      <c r="I182" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J182" s="11"/>
       <c r="K182" s="14"/>
       <c r="L182" s="14"/>
       <c r="M182" s="14"/>
@@ -21332,7 +19371,7 @@
       <c r="P182" s="14"/>
       <c r="Q182" s="15"/>
     </row>
-    <row r="183" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="11" t="n">
         <v>182</v>
       </c>
@@ -21340,16 +19379,16 @@
         <v>55</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G183" s="13" t="s">
         <v>52</v>
@@ -21369,7 +19408,7 @@
       <c r="P183" s="14"/>
       <c r="Q183" s="15"/>
     </row>
-    <row r="184" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="11" t="n">
         <v>183</v>
       </c>
@@ -21377,27 +19416,29 @@
         <v>59</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>387</v>
+        <v>467</v>
       </c>
       <c r="G184" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H184" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I184" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J184" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="K184" s="14"/>
       <c r="L184" s="14"/>
       <c r="M184" s="14"/>
@@ -21406,1099 +19447,27 @@
       <c r="P184" s="14"/>
       <c r="Q184" s="15"/>
     </row>
-    <row r="185" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="11" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C185" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="D185" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="E185" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F185" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G185" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H185" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I185" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="J185" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="K185" s="14"/>
-      <c r="L185" s="14"/>
-      <c r="M185" s="14"/>
-      <c r="N185" s="14"/>
-      <c r="O185" s="14"/>
-      <c r="P185" s="14"/>
-      <c r="Q185" s="15"/>
-    </row>
-    <row r="186" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="11" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C186" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="D186" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E186" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F186" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G186" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H186" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I186" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J186" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="K186" s="14"/>
-      <c r="L186" s="14"/>
-      <c r="M186" s="14"/>
-      <c r="N186" s="14"/>
-      <c r="O186" s="14"/>
-      <c r="P186" s="14"/>
-      <c r="Q186" s="15"/>
-    </row>
-    <row r="187" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="11" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C187" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="D187" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="E187" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F187" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G187" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H187" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I187" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J187" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="K187" s="14"/>
-      <c r="L187" s="14"/>
-      <c r="M187" s="14"/>
-      <c r="N187" s="14"/>
-      <c r="O187" s="14"/>
-      <c r="P187" s="14"/>
-      <c r="Q187" s="15"/>
-    </row>
-    <row r="188" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="11" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C188" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="D188" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="E188" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F188" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G188" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H188" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I188" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="J188" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="K188" s="14"/>
-      <c r="L188" s="14"/>
-      <c r="M188" s="14"/>
-      <c r="N188" s="14"/>
-      <c r="O188" s="14"/>
-      <c r="P188" s="14"/>
-      <c r="Q188" s="15"/>
-    </row>
-    <row r="189" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="11" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C189" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="E189" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F189" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G189" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H189" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I189" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J189" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="K189" s="14"/>
-      <c r="L189" s="14"/>
-      <c r="M189" s="14"/>
-      <c r="N189" s="14"/>
-      <c r="O189" s="14"/>
-      <c r="P189" s="14"/>
-      <c r="Q189" s="15"/>
-    </row>
-    <row r="190" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="11" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C190" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>498</v>
-      </c>
-      <c r="E190" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F190" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G190" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H190" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I190" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J190" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="K190" s="14"/>
-      <c r="L190" s="14"/>
-      <c r="M190" s="14"/>
-      <c r="N190" s="14"/>
-      <c r="O190" s="14"/>
-      <c r="P190" s="14"/>
-      <c r="Q190" s="15"/>
-    </row>
-    <row r="191" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="11" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C191" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="D191" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="E191" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F191" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G191" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H191" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I191" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J191" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="K191" s="14"/>
-      <c r="L191" s="14"/>
-      <c r="M191" s="14"/>
-      <c r="N191" s="14"/>
-      <c r="O191" s="14"/>
-      <c r="P191" s="14"/>
-      <c r="Q191" s="15"/>
-    </row>
-    <row r="192" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="11" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C192" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="D192" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="E192" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F192" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G192" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H192" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I192" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J192" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="K192" s="14"/>
-      <c r="L192" s="14"/>
-      <c r="M192" s="14"/>
-      <c r="N192" s="14"/>
-      <c r="O192" s="14"/>
-      <c r="P192" s="14"/>
-      <c r="Q192" s="15"/>
-    </row>
-    <row r="193" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="11" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C193" s="11" t="s">
-        <v>503</v>
-      </c>
-      <c r="D193" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="E193" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F193" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G193" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H193" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I193" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J193" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="K193" s="14"/>
-      <c r="L193" s="14"/>
-      <c r="M193" s="14"/>
-      <c r="N193" s="14"/>
-      <c r="O193" s="14"/>
-      <c r="P193" s="14"/>
-      <c r="Q193" s="15"/>
-    </row>
-    <row r="194" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="11" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C194" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="D194" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="E194" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F194" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G194" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H194" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I194" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="J194" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="K194" s="14"/>
-      <c r="L194" s="14"/>
-      <c r="M194" s="14"/>
-      <c r="N194" s="14"/>
-      <c r="O194" s="14"/>
-      <c r="P194" s="14"/>
-      <c r="Q194" s="15"/>
-    </row>
-    <row r="195" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="11" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C195" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="D195" s="11" t="s">
-        <v>508</v>
-      </c>
-      <c r="E195" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F195" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G195" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H195" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I195" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J195" s="11"/>
-      <c r="K195" s="14"/>
-      <c r="L195" s="14"/>
-      <c r="M195" s="14"/>
-      <c r="N195" s="14"/>
-      <c r="O195" s="14"/>
-      <c r="P195" s="14"/>
-      <c r="Q195" s="15"/>
-    </row>
-    <row r="196" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="11" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C196" s="11" t="s">
-        <v>509</v>
-      </c>
-      <c r="D196" s="12" t="s">
-        <v>510</v>
-      </c>
-      <c r="E196" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F196" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G196" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H196" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I196" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J196" s="11"/>
-      <c r="K196" s="14"/>
-      <c r="L196" s="14"/>
-      <c r="M196" s="14"/>
-      <c r="N196" s="14"/>
-      <c r="O196" s="14"/>
-      <c r="P196" s="14"/>
-      <c r="Q196" s="15"/>
-    </row>
-    <row r="197" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="11" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C197" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="D197" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="E197" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G197" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H197" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I197" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J197" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="K197" s="14"/>
-      <c r="L197" s="14"/>
-      <c r="M197" s="14"/>
-      <c r="N197" s="14"/>
-      <c r="O197" s="14"/>
-      <c r="P197" s="14"/>
-      <c r="Q197" s="15"/>
-    </row>
-    <row r="198" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="11" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C198" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="D198" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="E198" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F198" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G198" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H198" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I198" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J198" s="11"/>
-      <c r="K198" s="14"/>
-      <c r="L198" s="14"/>
-      <c r="M198" s="14"/>
-      <c r="N198" s="14"/>
-      <c r="O198" s="14"/>
-      <c r="P198" s="14"/>
-      <c r="Q198" s="15"/>
-    </row>
-    <row r="199" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="11" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C199" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="D199" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="E199" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F199" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G199" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H199" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I199" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J199" s="11"/>
-      <c r="K199" s="14"/>
-      <c r="L199" s="14"/>
-      <c r="M199" s="14"/>
-      <c r="N199" s="14"/>
-      <c r="O199" s="14"/>
-      <c r="P199" s="14"/>
-      <c r="Q199" s="15"/>
-    </row>
-    <row r="200" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="11" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C200" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="D200" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="E200" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F200" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G200" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H200" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I200" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J200" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="K200" s="14"/>
-      <c r="L200" s="14"/>
-      <c r="M200" s="14"/>
-      <c r="N200" s="14"/>
-      <c r="O200" s="14"/>
-      <c r="P200" s="14"/>
-      <c r="Q200" s="15"/>
-    </row>
-    <row r="201" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C201" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="D201" s="12" t="s">
-        <v>520</v>
-      </c>
-      <c r="E201" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F201" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="G201" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H201" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I201" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J201" s="11"/>
-      <c r="K201" s="14"/>
-      <c r="L201" s="14"/>
-      <c r="M201" s="14"/>
-      <c r="N201" s="14"/>
-      <c r="O201" s="14"/>
-      <c r="P201" s="14"/>
-      <c r="Q201" s="15"/>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="11" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C202" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="D202" s="11" t="s">
-        <v>522</v>
-      </c>
-      <c r="E202" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F202" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G202" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H202" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I202" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J202" s="11"/>
-      <c r="K202" s="14"/>
-      <c r="L202" s="14"/>
-      <c r="M202" s="14"/>
-      <c r="N202" s="14"/>
-      <c r="O202" s="14"/>
-      <c r="P202" s="14"/>
-      <c r="Q202" s="15"/>
-    </row>
-    <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="11" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C203" s="11" t="s">
-        <v>524</v>
-      </c>
-      <c r="D203" s="11" t="s">
-        <v>525</v>
-      </c>
-      <c r="E203" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F203" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G203" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H203" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I203" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J203" s="11"/>
-      <c r="K203" s="14"/>
-      <c r="L203" s="14"/>
-      <c r="M203" s="14"/>
-      <c r="N203" s="14"/>
-      <c r="O203" s="14"/>
-      <c r="P203" s="14"/>
-      <c r="Q203" s="15"/>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="11" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C204" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="D204" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="E204" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F204" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G204" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H204" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I204" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J204" s="11"/>
-      <c r="K204" s="14"/>
-      <c r="L204" s="14"/>
-      <c r="M204" s="14"/>
-      <c r="N204" s="14"/>
-      <c r="O204" s="14"/>
-      <c r="P204" s="14"/>
-      <c r="Q204" s="15"/>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="11" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C205" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="D205" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="E205" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F205" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G205" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H205" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I205" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J205" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="K205" s="14"/>
-      <c r="L205" s="14"/>
-      <c r="M205" s="14"/>
-      <c r="N205" s="14"/>
-      <c r="O205" s="14"/>
-      <c r="P205" s="14"/>
-      <c r="Q205" s="15"/>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="11" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C206" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="D206" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="E206" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F206" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G206" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H206" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I206" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J206" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="K206" s="14"/>
-      <c r="L206" s="14"/>
-      <c r="M206" s="14"/>
-      <c r="N206" s="14"/>
-      <c r="O206" s="14"/>
-      <c r="P206" s="14"/>
-      <c r="Q206" s="15"/>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="11" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C207" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="D207" s="11" t="s">
-        <v>533</v>
-      </c>
-      <c r="E207" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F207" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G207" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H207" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I207" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J207" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="K207" s="14"/>
-      <c r="L207" s="14"/>
-      <c r="M207" s="14"/>
-      <c r="N207" s="14"/>
-      <c r="O207" s="14"/>
-      <c r="P207" s="14"/>
-      <c r="Q207" s="15"/>
-    </row>
-    <row r="208" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="11" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C208" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="D208" s="11" t="s">
-        <v>535</v>
-      </c>
-      <c r="E208" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F208" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G208" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H208" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I208" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J208" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="K208" s="14"/>
-      <c r="L208" s="14"/>
-      <c r="M208" s="14"/>
-      <c r="N208" s="14"/>
-      <c r="O208" s="14"/>
-      <c r="P208" s="14"/>
-      <c r="Q208" s="15"/>
-    </row>
-    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="11" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C209" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="D209" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="E209" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F209" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G209" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H209" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I209" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J209" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="K209" s="14"/>
-      <c r="L209" s="14"/>
-      <c r="M209" s="14"/>
-      <c r="N209" s="14"/>
-      <c r="O209" s="14"/>
-      <c r="P209" s="14"/>
-      <c r="Q209" s="15"/>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C210" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="D210" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="E210" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F210" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G210" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H210" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I210" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J210" s="11"/>
-      <c r="K210" s="14"/>
-      <c r="L210" s="14"/>
-      <c r="M210" s="14"/>
-      <c r="N210" s="14"/>
-      <c r="O210" s="14"/>
-      <c r="P210" s="14"/>
-      <c r="Q210" s="15"/>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C211" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="D211" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="E211" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F211" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G211" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H211" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I211" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J211" s="11"/>
-      <c r="K211" s="14"/>
-      <c r="L211" s="14"/>
-      <c r="M211" s="14"/>
-      <c r="N211" s="14"/>
-      <c r="O211" s="14"/>
-      <c r="P211" s="14"/>
-      <c r="Q211" s="15"/>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="11" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C212" s="11" t="s">
-        <v>542</v>
-      </c>
-      <c r="D212" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="E212" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="F212" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G212" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H212" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I212" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J212" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="K212" s="14"/>
-      <c r="L212" s="14"/>
-      <c r="M212" s="14"/>
-      <c r="N212" s="14"/>
-      <c r="O212" s="14"/>
-      <c r="P212" s="14"/>
-      <c r="Q212" s="15"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q212"/>
-  <conditionalFormatting sqref="L2:L212">
+  <autoFilter ref="A1:Q184"/>
+  <conditionalFormatting sqref="L2:L184">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>AND(OR(L2="틀림",L2="일부 틀림"),M2="",N2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" error="관련 / 일부 관련 / 무관 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K212" type="list">
+    <dataValidation allowBlank="true" error="관련 / 일부 관련 / 무관 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K184" type="list">
       <formula1>"관련,일부 관련,무관"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="맞음 / 일부 틀림 / 틀림 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L212" type="list">
+    <dataValidation allowBlank="true" error="맞음 / 일부 틀림 / 틀림 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L184" type="list">
       <formula1>"맞음,일부 틀림,틀림"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="팀원A~D 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P2:P212" type="list">
+    <dataValidation allowBlank="true" error="팀원A~D 중에서 고르세요" errorStyle="stop" errorTitle="목록에서 고르세요" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P2:P184" type="list">
       <formula1>"팀원A,팀원B,팀원C,팀원D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="날짜(예: 2026-10-30)를 입력하세요" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q212" type="date">
+    <dataValidation allowBlank="true" error="날짜(예: 2026-10-30)를 입력하세요" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q184" type="date">
       <formula1>DATE(2026,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -22687,34 +19656,6 @@
     <hyperlink ref="G182" r:id="rId182" display="열기"/>
     <hyperlink ref="G183" r:id="rId183" display="열기"/>
     <hyperlink ref="G184" r:id="rId184" display="열기"/>
-    <hyperlink ref="G185" r:id="rId185" display="열기"/>
-    <hyperlink ref="G186" r:id="rId186" display="열기"/>
-    <hyperlink ref="G187" r:id="rId187" display="열기"/>
-    <hyperlink ref="G188" r:id="rId188" display="열기"/>
-    <hyperlink ref="G189" r:id="rId189" display="열기"/>
-    <hyperlink ref="G190" r:id="rId190" display="열기"/>
-    <hyperlink ref="G191" r:id="rId191" display="열기"/>
-    <hyperlink ref="G192" r:id="rId192" display="열기"/>
-    <hyperlink ref="G193" r:id="rId193" display="열기"/>
-    <hyperlink ref="G194" r:id="rId194" display="열기"/>
-    <hyperlink ref="G195" r:id="rId195" display="열기"/>
-    <hyperlink ref="G196" r:id="rId196" display="열기"/>
-    <hyperlink ref="G197" r:id="rId197" display="열기"/>
-    <hyperlink ref="G198" r:id="rId198" display="열기"/>
-    <hyperlink ref="G199" r:id="rId199" display="열기"/>
-    <hyperlink ref="G200" r:id="rId200" display="열기"/>
-    <hyperlink ref="G201" r:id="rId201" display="열기"/>
-    <hyperlink ref="G202" r:id="rId202" display="열기"/>
-    <hyperlink ref="G203" r:id="rId203" display="열기"/>
-    <hyperlink ref="G204" r:id="rId204" display="열기"/>
-    <hyperlink ref="G205" r:id="rId205" display="열기"/>
-    <hyperlink ref="G206" r:id="rId206" display="열기"/>
-    <hyperlink ref="G207" r:id="rId207" display="열기"/>
-    <hyperlink ref="G208" r:id="rId208" display="열기"/>
-    <hyperlink ref="G209" r:id="rId209" display="열기"/>
-    <hyperlink ref="G210" r:id="rId210" display="열기"/>
-    <hyperlink ref="G211" r:id="rId211" display="열기"/>
-    <hyperlink ref="G212" r:id="rId212" display="열기"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22723,8 +19664,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId213"/>
-  <legacyDrawing r:id="rId214"/>
+  <drawing r:id="rId185"/>
+  <legacyDrawing r:id="rId186"/>
 </worksheet>
 </file>
 
@@ -22759,7 +19700,7 @@
         <v>37</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>38</v>
@@ -22801,19 +19742,19 @@
         <v>46</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>545</v>
+        <v>489</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>546</v>
+        <v>490</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>547</v>
+        <v>491</v>
       </c>
       <c r="S1" s="10" t="s">
-        <v>548</v>
+        <v>492</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>549</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22850,11 +19791,11 @@
         <v>47</v>
       </c>
       <c r="Q2" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C2,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C2,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C2,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C2,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R2" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C2,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C2,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C2,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C2,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S2" s="11" t="str">
@@ -22902,11 +19843,11 @@
         <v>63</v>
       </c>
       <c r="Q3" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C3,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C3,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C3,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C3,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R3" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C3,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C3,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C3,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C3,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S3" s="11" t="str">
@@ -22954,11 +19895,11 @@
         <v>47</v>
       </c>
       <c r="Q4" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C4,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C4,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C4,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C4,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R4" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C4,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C4,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C4,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C4,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S4" s="11" t="str">
@@ -23006,11 +19947,11 @@
         <v>59</v>
       </c>
       <c r="Q5" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C5,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C5,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C5,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C5,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R5" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C5,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C5,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C5,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C5,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S5" s="11" t="str">
@@ -23058,11 +19999,11 @@
         <v>47</v>
       </c>
       <c r="Q6" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C6,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C6,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C6,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C6,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R6" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C6,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C6,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C6,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C6,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S6" s="11" t="str">
@@ -23108,11 +20049,11 @@
         <v>59</v>
       </c>
       <c r="Q7" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C7,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C7,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C7,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C7,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R7" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C7,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C7,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C7,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C7,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S7" s="11" t="str">
@@ -23160,11 +20101,11 @@
         <v>55</v>
       </c>
       <c r="Q8" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C8,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C8,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C8,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C8,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R8" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C8,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C8,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C8,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C8,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S8" s="11" t="str">
@@ -23184,10 +20125,10 @@
         <v>63</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>74</v>
@@ -23196,10 +20137,10 @@
         <v>52</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
@@ -23209,14 +20150,14 @@
       <c r="N9" s="14"/>
       <c r="O9" s="15"/>
       <c r="P9" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q9" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C9,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C9,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C9,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C9,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R9" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C9,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C9,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C9,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C9,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S9" s="11" t="str">
@@ -23233,13 +20174,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>226</v>
+        <v>200</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>74</v>
@@ -23248,10 +20189,10 @@
         <v>52</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
@@ -23261,14 +20202,14 @@
       <c r="N10" s="14"/>
       <c r="O10" s="15"/>
       <c r="P10" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Q10" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C10,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C10,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C10,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C10,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R10" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C10,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C10,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C10,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C10,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S10" s="11" t="str">
@@ -23285,13 +20226,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>249</v>
+        <v>202</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>74</v>
@@ -23300,10 +20241,10 @@
         <v>52</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
@@ -23313,14 +20254,14 @@
       <c r="N11" s="14"/>
       <c r="O11" s="15"/>
       <c r="P11" s="12" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C11,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C11,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C11,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C11,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R11" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C11,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C11,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C11,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C11,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S11" s="11" t="str">
@@ -23340,10 +20281,10 @@
         <v>59</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>257</v>
+        <v>223</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>74</v>
@@ -23352,10 +20293,10 @@
         <v>52</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
@@ -23365,14 +20306,14 @@
       <c r="N12" s="14"/>
       <c r="O12" s="15"/>
       <c r="P12" s="12" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C12,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C12,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C12,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C12,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R12" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C12,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C12,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C12,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C12,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S12" s="11" t="str">
@@ -23392,10 +20333,10 @@
         <v>63</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>74</v>
@@ -23404,10 +20345,10 @@
         <v>52</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -23420,11 +20361,11 @@
         <v>59</v>
       </c>
       <c r="Q13" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C13,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C13,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C13,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C13,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R13" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C13,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C13,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C13,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C13,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S13" s="11" t="str">
@@ -23444,13 +20385,13 @@
         <v>47</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>52</v>
@@ -23472,11 +20413,11 @@
         <v>55</v>
       </c>
       <c r="Q14" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C14,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C14,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C14,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C14,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R14" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C14,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C14,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C14,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C14,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S14" s="11" t="str">
@@ -23496,22 +20437,22 @@
         <v>55</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>358</v>
+        <v>302</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -23524,11 +20465,11 @@
         <v>63</v>
       </c>
       <c r="Q15" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C15,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C15,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C15,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C15,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R15" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C15,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C15,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C15,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C15,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S15" s="11" t="str">
@@ -23548,13 +20489,13 @@
         <v>59</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>364</v>
+        <v>308</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>52</v>
@@ -23563,7 +20504,7 @@
         <v>94</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>365</v>
+        <v>309</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -23576,11 +20517,11 @@
         <v>55</v>
       </c>
       <c r="Q16" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C16,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C16,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C16,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C16,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R16" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C16,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C16,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C16,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C16,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S16" s="11" t="str">
@@ -23600,13 +20541,13 @@
         <v>63</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>374</v>
+        <v>318</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>52</v>
@@ -23615,7 +20556,7 @@
         <v>103</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -23628,11 +20569,11 @@
         <v>55</v>
       </c>
       <c r="Q17" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C17,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C17,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C17,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C17,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R17" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C17,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C17,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C17,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C17,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S17" s="11" t="str">
@@ -23652,22 +20593,22 @@
         <v>47</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>434</v>
+        <v>378</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
@@ -23680,11 +20621,11 @@
         <v>63</v>
       </c>
       <c r="Q18" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C18,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C18,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C18,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C18,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R18" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C18,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C18,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C18,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C18,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S18" s="11" t="str">
@@ -23704,13 +20645,13 @@
         <v>55</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>466</v>
+        <v>410</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>467</v>
+        <v>411</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>52</v>
@@ -23719,7 +20660,7 @@
         <v>33</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>468</v>
+        <v>412</v>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
@@ -23732,11 +20673,11 @@
         <v>63</v>
       </c>
       <c r="Q19" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C19,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C19,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C19,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C19,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R19" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C19,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C19,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C19,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C19,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S19" s="11" t="str">
@@ -23756,22 +20697,22 @@
         <v>59</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>483</v>
+        <v>427</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>484</v>
+        <v>428</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>485</v>
+        <v>429</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>486</v>
+        <v>430</v>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
@@ -23784,11 +20725,11 @@
         <v>63</v>
       </c>
       <c r="Q20" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C20,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C20,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C20,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C20,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R20" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C20,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C20,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C20,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C20,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S20" s="11" t="str">
@@ -23808,22 +20749,22 @@
         <v>63</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>491</v>
+        <v>435</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>492</v>
+        <v>436</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>493</v>
+        <v>437</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>494</v>
+        <v>438</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
@@ -23836,11 +20777,11 @@
         <v>59</v>
       </c>
       <c r="Q21" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$212,MATCH($C21,검수!$C$2:$C$212,0))="","",INDEX(검수!$K$2:$K$212,MATCH($C21,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$K$2:$K$184,MATCH($C21,검수!$C$2:$C$184,0))="","",INDEX(검수!$K$2:$K$184,MATCH($C21,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="R21" s="11" t="str">
-        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$212,MATCH($C21,검수!$C$2:$C$212,0))="","",INDEX(검수!$L$2:$L$212,MATCH($C21,검수!$C$2:$C$212,0))),"")</f>
+        <f aca="false">IFERROR(IF(INDEX(검수!$L$2:$L$184,MATCH($C21,검수!$C$2:$C$184,0))="","",INDEX(검수!$L$2:$L$184,MATCH($C21,검수!$C$2:$C$184,0))),"")</f>
         <v/>
       </c>
       <c r="S21" s="11" t="str">
@@ -23919,30 +20860,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>550</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>551</v>
+        <v>495</v>
       </c>
       <c r="B3" s="19" t="n">
-        <f aca="false">COUNTA(검수!$C$2:$C$212)</f>
-        <v>211</v>
+        <f aca="false">COUNTA(검수!$C$2:$C$184)</f>
+        <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="B4" s="19" t="n">
-        <f aca="false">COUNTA(검수!$L$2:$L$212)</f>
+        <f aca="false">COUNTA(검수!$L$2:$L$184)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>553</v>
+        <v>497</v>
       </c>
       <c r="B5" s="20" t="n">
         <f aca="false">IF(B3=0,0,B4/B3)</f>
@@ -23954,18 +20895,18 @@
         <v>30</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>554</v>
+        <v>498</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>555</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>556</v>
+        <v>500</v>
       </c>
       <c r="B8" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$L$2:$L$212,A8)</f>
+        <f aca="false">COUNTIF(검수!$L$2:$L$184,A8)</f>
         <v>0</v>
       </c>
       <c r="C8" s="20" t="n">
@@ -23978,7 +20919,7 @@
         <v>31</v>
       </c>
       <c r="B9" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$L$2:$L$212,A9)</f>
+        <f aca="false">COUNTIF(검수!$L$2:$L$184,A9)</f>
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
@@ -23988,10 +20929,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>557</v>
+        <v>501</v>
       </c>
       <c r="B10" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$L$2:$L$212,A10)</f>
+        <f aca="false">COUNTIF(검수!$L$2:$L$184,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="20" t="n">
@@ -24004,7 +20945,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>554</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24012,59 +20953,59 @@
         <v>29</v>
       </c>
       <c r="B13" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$K$2:$K$212,A13)</f>
+        <f aca="false">COUNTIF(검수!$K$2:$K$184,A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>558</v>
+        <v>502</v>
       </c>
       <c r="B14" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$K$2:$K$212,A14)</f>
+        <f aca="false">COUNTIF(검수!$K$2:$K$184,A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>559</v>
+        <v>503</v>
       </c>
       <c r="B15" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$K$2:$K$212,A15)</f>
+        <f aca="false">COUNTIF(검수!$K$2:$K$184,A15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>560</v>
+        <v>504</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>561</v>
+        <v>505</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>562</v>
+        <v>506</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>556</v>
+        <v>500</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>563</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>493</v>
+        <v>437</v>
       </c>
       <c r="B18" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A18&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A18&amp;"*")</f>
         <v>1</v>
       </c>
       <c r="C18" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A18&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A18&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D18" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A18&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A18&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E18" s="20" t="n">
@@ -24074,18 +21015,18 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="B19" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A19&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A19&amp;"*")</f>
         <v>1</v>
       </c>
       <c r="C19" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A19&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A19&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D19" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A19&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A19&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E19" s="20" t="n">
@@ -24098,15 +21039,15 @@
         <v>108</v>
       </c>
       <c r="B20" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A20&amp;"*")</f>
-        <v>48</v>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A20&amp;"*")</f>
+        <v>20</v>
       </c>
       <c r="C20" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A20&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A20&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D20" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A20&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A20&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E20" s="20" t="n">
@@ -24119,15 +21060,15 @@
         <v>167</v>
       </c>
       <c r="B21" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A21&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A21&amp;"*")</f>
         <v>12</v>
       </c>
       <c r="C21" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A21&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A21&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D21" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A21&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A21&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E21" s="20" t="n">
@@ -24140,15 +21081,15 @@
         <v>103</v>
       </c>
       <c r="B22" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A22&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A22&amp;"*")</f>
         <v>21</v>
       </c>
       <c r="C22" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A22&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A22&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D22" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A22&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A22&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E22" s="20" t="n">
@@ -24161,15 +21102,15 @@
         <v>33</v>
       </c>
       <c r="B23" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A23&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A23&amp;"*")</f>
         <v>2</v>
       </c>
       <c r="C23" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A23&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A23&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D23" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A23&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A23&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E23" s="20" t="n">
@@ -24179,18 +21120,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="B24" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A24&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A24&amp;"*")</f>
         <v>18</v>
       </c>
       <c r="C24" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A24&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A24&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D24" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A24&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A24&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E24" s="20" t="n">
@@ -24200,18 +21141,18 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>565</v>
+        <v>509</v>
       </c>
       <c r="B25" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A25&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A25&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="C25" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A25&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A25&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D25" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A25&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A25&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E25" s="20" t="n">
@@ -24224,15 +21165,15 @@
         <v>94</v>
       </c>
       <c r="B26" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"*"&amp;A26&amp;"*")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"*"&amp;A26&amp;"*")</f>
         <v>26</v>
       </c>
       <c r="C26" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A26&amp;"*",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A26&amp;"*",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D26" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"*"&amp;A26&amp;"*",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"*"&amp;A26&amp;"*",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E26" s="20" t="n">
@@ -24245,15 +21186,15 @@
         <v>54</v>
       </c>
       <c r="B27" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$I$2:$I$212,"(없음)")</f>
+        <f aca="false">COUNTIF(검수!$I$2:$I$184,"(없음)")</f>
         <v>87</v>
       </c>
       <c r="C27" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"(없음)",검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"(없음)",검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D27" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$I$2:$I$212,"(없음)",검수!$L$2:$L$212,"맞음")</f>
+        <f aca="false">COUNTIFS(검수!$I$2:$I$184,"(없음)",검수!$L$2:$L$184,"맞음")</f>
         <v>0</v>
       </c>
       <c r="E27" s="20" t="n">
@@ -24263,27 +21204,27 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>566</v>
+        <v>510</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>567</v>
+        <v>511</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>568</v>
+        <v>512</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>553</v>
+        <v>497</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>569</v>
+        <v>513</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24291,11 +21232,11 @@
         <v>47</v>
       </c>
       <c r="B31" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$212,A31)</f>
-        <v>53</v>
+        <f aca="false">COUNTIF(검수!$B$2:$B$184,A31)</f>
+        <v>46</v>
       </c>
       <c r="C31" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A31,검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$184,A31,검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D31" s="20" t="n">
@@ -24316,11 +21257,11 @@
         <v>55</v>
       </c>
       <c r="B32" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$212,A32)</f>
-        <v>53</v>
+        <f aca="false">COUNTIF(검수!$B$2:$B$184,A32)</f>
+        <v>46</v>
       </c>
       <c r="C32" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A32,검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$184,A32,검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D32" s="20" t="n">
@@ -24341,11 +21282,11 @@
         <v>59</v>
       </c>
       <c r="B33" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$212,A33)</f>
-        <v>53</v>
+        <f aca="false">COUNTIF(검수!$B$2:$B$184,A33)</f>
+        <v>46</v>
       </c>
       <c r="C33" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A33,검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$184,A33,검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D33" s="20" t="n">
@@ -24366,11 +21307,11 @@
         <v>63</v>
       </c>
       <c r="B34" s="21" t="n">
-        <f aca="false">COUNTIF(검수!$B$2:$B$212,A34)</f>
-        <v>52</v>
+        <f aca="false">COUNTIF(검수!$B$2:$B$184,A34)</f>
+        <v>45</v>
       </c>
       <c r="C34" s="21" t="n">
-        <f aca="false">COUNTIFS(검수!$B$2:$B$212,A34,검수!$L$2:$L$212,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(검수!$B$2:$B$184,A34,검수!$L$2:$L$184,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D34" s="20" t="n">
@@ -24388,12 +21329,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>570</v>
+        <v>514</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>571</v>
+        <v>515</v>
       </c>
       <c r="B38" s="21" t="n">
         <f aca="false">COUNTA(교차검수!$C$2:$C$21)</f>
@@ -24402,7 +21343,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>572</v>
+        <v>516</v>
       </c>
       <c r="B39" s="21" t="n">
         <f aca="false">SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;"")))</f>
@@ -24411,7 +21352,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>573</v>
+        <v>517</v>
       </c>
       <c r="B40" s="21" t="n">
         <f aca="false">SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21=교차검수!$J$2:$J$21))</f>
@@ -24420,7 +21361,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>563</v>
+        <v>507</v>
       </c>
       <c r="B41" s="20" t="n">
         <f aca="false">IF(B39=0,0,B40/B39)</f>
@@ -24429,7 +21370,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>574</v>
+        <v>518</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">IF(B39=0,0,(SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21="맞음"))*SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$J$2:$J$21="맞음"))+SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21="일부 틀림"))*SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$J$2:$J$21="일부 틀림"))+SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$R$2:$R$21="틀림"))*SUMPRODUCT(((교차검수!$R$2:$R$21&lt;&gt;"")*(교차검수!$J$2:$J$21&lt;&gt;""))*(교차검수!$J$2:$J$21="틀림")))/B39^2)</f>
@@ -24438,7 +21379,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>575</v>
+        <v>519</v>
       </c>
       <c r="B43" s="24" t="str">
         <f aca="false">IF(OR(B39=0,B42=1),"-",(B41-B42)/(1-B42))</f>
@@ -24447,7 +21388,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>576</v>
+        <v>520</v>
       </c>
       <c r="B44" s="20" t="n">
         <f aca="false">IF(SUMPRODUCT((교차검수!$Q$2:$Q$21&lt;&gt;"")*(교차검수!$I$2:$I$21&lt;&gt;""))=0,0,SUMPRODUCT((교차검수!$Q$2:$Q$21&lt;&gt;"")*(교차검수!$I$2:$I$21&lt;&gt;"")*(교차검수!$Q$2:$Q$21=교차검수!$I$2:$I$21))/SUMPRODUCT((교차검수!$Q$2:$Q$21&lt;&gt;"")*(교차검수!$I$2:$I$21&lt;&gt;"")))</f>
@@ -24456,7 +21397,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>577</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -24485,112 +21426,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>578</v>
+        <v>522</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>580</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>493</v>
+        <v>437</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>582</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>584</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>585</v>
+        <v>529</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>586</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>587</v>
+        <v>531</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>167</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>588</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>589</v>
+        <v>533</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>590</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>591</v>
+        <v>535</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>592</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>593</v>
+        <v>537</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>594</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>595</v>
+        <v>539</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>565</v>
+        <v>509</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>596</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>597</v>
+        <v>541</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>94</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>598</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
